--- a/results/scraped_Cape_Town_Youth_and_Tutoring.xlsx
+++ b/results/scraped_Cape_Town_Youth_and_Tutoring.xlsx
@@ -49,85 +49,85 @@
     <t>Youth| Official Trailer | HBO Max - YouTube</t>
   </si>
   <si>
+    <t>'Youth': Premiere Date, Trailer, Cast, Plot, and More Details</t>
+  </si>
+  <si>
     <t>Youth(2026) - IMDb</t>
   </si>
   <si>
+    <t>Youth(TV series) - Wikipedia</t>
+  </si>
+  <si>
     <t>YOUTHDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>'Youth': Premiere Date, Trailer, Cast, Plot, and More Details</t>
-  </si>
-  <si>
-    <t>Youth(TV series) - Wikipedia</t>
+    <t>'Youth' Sharon Horgan HBO Review: Stream It Or Skip It? - Decider</t>
+  </si>
+  <si>
+    <t>'Youth' Season 2: Cast, Premiere Date, Plot, and More Details</t>
   </si>
   <si>
     <t>Home |Youth.gov</t>
   </si>
   <si>
-    <t>YouthSeason 1 Trailer - YouTube</t>
-  </si>
-  <si>
-    <t>YOUTH| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Tutoring Clubs Of Las Vegas-TutoringClub</t>
-  </si>
-  <si>
-    <t>THE BEST 10 Tutoring Centers in LAS VEGAS,NV- Yelp</t>
-  </si>
-  <si>
-    <t>Tutoring| Student Success | UNLV</t>
-  </si>
-  <si>
-    <t>Private tutors inLas Vegas(Nevada) - Top tutors from 10$/hr</t>
-  </si>
-  <si>
-    <t>Las Vegas, West Sylvan LearningTutoringCenter | Personalized</t>
+    <t>Tutoringand Academic Support | STLCC</t>
   </si>
   <si>
     <t>Tutoringand Test Prep for K–12, Higher Education, and Career</t>
   </si>
   <si>
-    <t>Top 15 Tutorsin Las Vegas, NV- Vetted and Reviewed</t>
-  </si>
-  <si>
-    <t>BEST Tutors Near Me inLas Vegas,NV| Find Local Tutors</t>
-  </si>
-  <si>
-    <t>SapienceTutoring: Empowering Student Success throughoutLas Vegas</t>
-  </si>
-  <si>
-    <t>In-Home &amp; OnlineLas VegasTutors - Club Z!Tutoring</t>
+    <t>Top 15 Tutors inSt. Louis,MO- Vetted and Reviewed</t>
+  </si>
+  <si>
+    <t>Private tutors inSt. Louis(Missouri) - Top tutors from 10$/hr</t>
+  </si>
+  <si>
+    <t>OnlineTutoring-St. LouisCounty Library</t>
+  </si>
+  <si>
+    <t>In HomeTutoring&amp; OnlineTutoring-Club Z! Tutoring of Saint Louis,MO</t>
+  </si>
+  <si>
+    <t>OnlineTutoringFor Every Grade Level | K12Tutoring</t>
+  </si>
+  <si>
+    <t>100Tutoring Jobs, Employmentin St. Louis, MO| Indeed</t>
+  </si>
+  <si>
+    <t>K-12 PersonalizedTutoring&amp; SAT/ACT Prep inSt. Louis,MO</t>
+  </si>
+  <si>
+    <t>DarrTutoring- ACT, SAT, math, science tutors and classes inSt. Louis</t>
   </si>
   <si>
     <t>After(film series) -Wikipedia</t>
   </si>
   <si>
+    <t>After streaming:where to watchmovie online? - JustWatch</t>
+  </si>
+  <si>
     <t>AfterMovies in Order Chronologically and by Release Date</t>
   </si>
   <si>
+    <t>After(2019) - Full cast &amp; crew - IMDb</t>
+  </si>
+  <si>
     <t>After (2019 film) -Wikipedia</t>
   </si>
   <si>
-    <t>After streaming:where to watchmovie online? - JustWatch</t>
-  </si>
-  <si>
-    <t>After(2019) - Full cast &amp; crew - IMDb</t>
-  </si>
-  <si>
     <t>Watch After|Netflix</t>
   </si>
   <si>
-    <t>Buy Now Pay Later withAfterpay</t>
-  </si>
-  <si>
     <t>After- Where to Watch, Stream, Rent, or Buy |Moviefone</t>
   </si>
   <si>
+    <t>AfterFull’High-Quality’ Movie HD | Videos &amp; Movies onVimeo</t>
+  </si>
+  <si>
     <t>All 5 'After' Movies in Order - Fiction Horizon</t>
   </si>
   <si>
-    <t>AFTER Definition&amp; Meaning -Merriam-Webster</t>
+    <t>After| Full Movie | Movies Anywhere</t>
   </si>
   <si>
     <t>Literacy-Wikipedia</t>
@@ -136,25 +136,25 @@
     <t>Literacy| Definition, History, &amp; Facts | Britannica</t>
   </si>
   <si>
+    <t>LITERACYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
     <t>Literacy: what you need to know - UNESCO</t>
   </si>
   <si>
-    <t>LITERACYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Home -LiteracyTexas</t>
-  </si>
-  <si>
     <t>LiteracyRate in the US 2026 | By Year &amp; State Stats</t>
   </si>
   <si>
+    <t>LITERACY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>What isLiteracy? Meaning, Definition. - UNESCO</t>
   </si>
   <si>
     <t>Literacy- Our World in Data</t>
   </si>
   <si>
-    <t>LITERACY| English meaning - Cambridge Dictionary</t>
+    <t>What’s driving decline in U.S.literacyrates? — Harvard Gazette</t>
   </si>
   <si>
     <t>What isLiteracy? (with pictures) - Language Humanities</t>
@@ -166,30 +166,30 @@
     <t>Homework- Wikipedia</t>
   </si>
   <si>
+    <t>Sign in - Google Accounts</t>
+  </si>
+  <si>
+    <t>Gauth - Best AIHomeworkHelper for All School Subjects</t>
+  </si>
+  <si>
     <t>Free AIHomeworkHelper, Step-by-step &amp; No Sign-up| StudyX</t>
   </si>
   <si>
-    <t>Sign in - Google Accounts</t>
-  </si>
-  <si>
-    <t>Gauth - Best AIHomeworkHelper for All School Subjects</t>
-  </si>
-  <si>
     <t>IXL | Math, Language Arts, Science, Social Studies, and Spanish</t>
   </si>
   <si>
+    <t>HomeworkAI - Your AIHomeworkHelper</t>
+  </si>
+  <si>
+    <t>Free AIHomeworkHelper Online</t>
+  </si>
+  <si>
     <t>Homeworkify - Fully FreeHomeworkHelper Tool by AI Tutor</t>
   </si>
   <si>
-    <t>Brainly for Parents: AIHomeworkHelp &amp; Test Prep, Grades 9–12</t>
-  </si>
-  <si>
     <t>Free AIHomeworkHelper, No Sign-Up - Edubrain.ai</t>
   </si>
   <si>
-    <t>HomeworkAI - Your AIHomeworkHelper</t>
-  </si>
-  <si>
     <t>The 12 Characteristics of a Good Leader | CCL</t>
   </si>
   <si>
@@ -250,64 +250,64 @@
     <t>A Future Built onMentorship: Why Mentoring is the Essential ...</t>
   </si>
   <si>
-    <t>Jobsat Article| Article Careers</t>
-  </si>
-  <si>
-    <t>Senior Manager, Global Sourcing | Article Careers</t>
-  </si>
-  <si>
-    <t>Business Support Officer - People and Culture - Home based /Reading...</t>
-  </si>
-  <si>
-    <t>Full Stack Engineer - Remote (select US states) | Coforma Careers</t>
-  </si>
-  <si>
-    <t>Associate Manager, TeenReadingAmbassadors (Temporary)</t>
-  </si>
-  <si>
-    <t>Winter 2026 Production Engineering Intern - Hawthorne, California ...</t>
-  </si>
-  <si>
-    <t>Careers | HarperCollins UK Careers</t>
-  </si>
-  <si>
-    <t>Our Approach to AI in Recruitment | Pinpoint</t>
-  </si>
-  <si>
-    <t>Industrial Designer - Hawthorne, California | Astrolab Careers</t>
-  </si>
-  <si>
-    <t>AI ATS: AI Applicant Tracking System | Pinpoint</t>
+    <t>Teach Your Child To Read Early, Step by Step |Reading.com</t>
+  </si>
+  <si>
+    <t>ReadingEggs</t>
+  </si>
+  <si>
+    <t>Reading A-Z: The onlinereadingprogram with downloadable books to ...</t>
+  </si>
+  <si>
+    <t>Reading- Wikipedia</t>
+  </si>
+  <si>
+    <t>Reading, Berkshire- Wikipedia</t>
+  </si>
+  <si>
+    <t>ReadingRockets: Launching YoungReaders</t>
+  </si>
+  <si>
+    <t>READINGDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>What IsReading? -ReadingRockets</t>
+  </si>
+  <si>
+    <t>WhyReadingMatters: What Neuroscience Reveals</t>
+  </si>
+  <si>
+    <t>Practise Englishreadingskills | LearnEnglish</t>
   </si>
   <si>
     <t>Education.com | #1EducationalSite for Pre-K to 8th Grade</t>
   </si>
   <si>
+    <t>Education-Wikipedia</t>
+  </si>
+  <si>
+    <t>Home| U.S. Department of Education</t>
+  </si>
+  <si>
     <t>EDUCATIONALDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Education-Wikipedia</t>
-  </si>
-  <si>
     <t>Definition, Development, History, Types, &amp; Facts - Britannica</t>
   </si>
   <si>
     <t>EDUCATIONAL| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Home| U.S. Department of Education</t>
-  </si>
-  <si>
-    <t>EDUCATIONALDefinition &amp; Meaning | Dictionary.com</t>
-  </si>
-  <si>
-    <t>EDUCATIONAL| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>Educational- definition ofeducationalby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>EducationalGames | Education.com</t>
+    <t>EDUCATIONDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Worksheets,EducationalGames, Printables, and Activities</t>
+  </si>
+  <si>
+    <t>Educational Games- Play Online for Free! - Poki</t>
+  </si>
+  <si>
+    <t>Edutopia- What Works in Education</t>
   </si>
   <si>
     <t>Youth &amp; Tutoring</t>
@@ -316,274 +316,274 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3adc90e80af4f6b832a875250cbcc0cc44634acf8f13d448d0c9e39abc4bb35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1bd69344bd9664a4ac163ce139221bf494525f66ffa287f31c1367599f232c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef0e88c634239ab3f1d72cd1a7ef6936734e84ce731f59f0b6cffbca34660a5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5896309f95a37be55b4d1b0104c154463f29564c6367ea19a5bd4db3323004d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee8ebef88eb73055c06d0ec3e02ac2832eeabf99465c5688d8111af448ceb9b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32398bd8e5b7103b590ce120cf886fd982a5062628caf43f4f04e69a228dbf6eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3986deb74b790dd87dc4b305f979e33b173e565a7c3acefe552c322af4fe937aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0abab53fe0e5cf5237df855e7f40fcfa9565c2614b64a4ac78e5af281310f9d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4351f7a1adcfffb619560023e5228d0fbe692fc49b06f93e9a38a795db6dc8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0yeGh0Q19pV2NnWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62b97a42a793899c4230a26cbdfb0047e5071f52068ee5e74f4770e5bc852f5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0065c788-9109-67c0-1ace-d06a90ed66d9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3lvdXRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75fc117bda08b9c3480e0e8c2fff6ca1b02665df9a07df78f570e67b039352a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly90dXRvcmluZ2NsdWIuY29tL3ZlZ2FzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7cb5d81ae9f08fb143c9413b3ab65156d7f88c5e0e38f1ecc43ae6b28ef88f56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9dHV0b3JpbmcmZmluZF9sb2M9TGFzK1ZlZ2FzJTJDK05WJm1zb2NraWQ9MDVjYWJkOWM1OWM5NjExMzA4MjhhYTdlNTg2MjYwNDA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c638cee65a176084f0e223f6f8e37a41f0d6a719dc46b9b0b7671bd994df5acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cudW5sdi5lZHUvc3R1ZGVudHN1Y2Nlc3Mvc2VydmljZXMvdHV0b3Jpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e114284de716ac7d9318f12a08204d297ab07c1b25a7920b5c09a7218507523JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwcm9mLmNvbS9sZXNzb25zL2FsbC10dXRvcnMvbGFzLXZlZ2FzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a308fb29df35b220500d17d83e7c8ec06d994548f5b747c5999030a7f708b130JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cuc3lsdmFubGVhcm5pbmcuY29tL2xvY2F0aW9ucy91cy9udi9sYXMtdmVnYXMtdHV0b3JpbmcvbGFzLXZlZ2FzLXdlc3Qv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff2a7a126a229b70b9d41307de3616b07f305e2243cbd9faa30f31a412d0fd62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cudHV0b3IuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=524e67f7190481d4e6956b9b913e868cb503a0b81e5553f16f42d80a27be7dc3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cudmFyc2l0eXR1dG9ycy5jb20vdC9uZXZhZGEvbGFzLXZlZ2Fz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c119a744eb7d263a6cc62beff17e85e8dbcb43e47242c7193736a86ba74a460aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly93d3cuY2FyZS5jb20vdHV0b3JzL2xhcy12ZWdhcy1udg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe175afb510d0e530c47fdb57913389dce22e4c10d4c33f0c4b0e5a0442962ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly90aGVzYXBpZW5jZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c876b8c836d18c7b6d132cfa5967cd2d9eb39654079e581a85b69b50904b577bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05cabd9c-59c9-6113-0828-aa7e58626040&amp;u=a1aHR0cHM6Ly90dXRvcnMuY2x1Ynp0dXRvcmluZy5jb20vbGFzLXZlZ2FzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a3ca0dd69c178d7ea43e825e832708864970a33f77d3077bc80963146753f51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfKGZpbG1fc2VyaWVzKQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cf49ed65ef9f810ce58537cd7ec1c8238c4b77dceca166aa06d2d2141555174JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly9tb3ZpZXdlYi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c636686b4a5837dc38362bea72d0606c452d33570c58d195050b0b6ee7273d61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfJTI4MjAxOV9maWxtJTI5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c3b3b95afc644fcf6c2f42f2e71bc238acfcd528c61048fb4b918f81548aceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9hZnRlci0yMDE5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b51d16e1ff81be968bdb46da98ff2e379b5fdd38eae9c06bf47d11d41e9d7fb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ0MTI2NDc2L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cac33165718980b40f2a133ec9350bd509d62863802526c2ae0aa9c97bdcf817JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODAyNDQzMTE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef7549a0b9fa2e1042862f6df1d8a0d77e9fca59eedaf59d54730723c4f0e6bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cuYWZ0ZXJwYXkuY29tL2VuLUFV&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a898238e904c1f7687216fa267574ecc2fbe7a38d291dbfb2d03777b04b21ed8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L3doZXJlLXRvLXdhdGNoLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c482ca05303c6e5a305914ee28fab4151d26947a58f1158530698272150a0d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly9maWN0aW9uaG9yaXpvbi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f64507a67429f5c05eef94f1ccf2087531c328f05711f4ff6f830c21977c3c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22a6cf6f-2d9f-6e01-0214-d88d2c386fb4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FmdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ef7eb216bedca19e7955c4ae32d657a66b34f29864592843f83cc4c309464dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be44974f85e6db84e3449cd8c298f68f4ecab538d2981fc2448a83281cf4f714JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=133cae42914f2bd4acaf21ee14a151499ff08bef0e02cda73cbed3784f45caa2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeS9uZWVkLWtub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1494968dd514f8c63e34a8bf37c75941277a7acdb64423032d7f29b8700900d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2xpdGVyYWN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b62863027631bf12a1762d5a9b39dcf4dc4f97048f66261765560e75b6d4ef0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cubGl0ZXJhY3l0ZXhhcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9500f3dace1637b5fc3a129ed2d0c28f8347a98670f7d83fd73afed48149af5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cudGhlZ2xvYmFsc3RhdGlzdGljcy5jb20vbGl0ZXJhY3ktcmF0ZS1pbi10aGUtdW5pdGVkLXN0YXRlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b70f952d093845a75c8c6975119aa62af73bab7f57f0a4cd573a9579589cdbebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9xdWVyeS1saXN0L2wvbGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1711c22558c3d6a23a1e1aeb01c7cf486ef51c879701ae61daed974daed7def6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly9vdXJ3b3JsZGluZGF0YS5vcmcvbGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fa2aeb4a81a0d9e51a16d250ce1d93812e11fa4c14a2fcec277518a80a6ce5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2xpdGVyYWN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63136e17fa9b16101e01a5f98e0d415ac7499b4dccdae68b93ae0c5cf2a1a4e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13ea3390-20a1-642c-3d45-24722126655c&amp;u=a1aHR0cHM6Ly93d3cubGFuZ3VhZ2VodW1hbml0aWVzLm9yZy93aGF0LWlzLWxpdGVyYWN5Lmh0bQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd19e7d4ef3daa856b86a3bab11c979d50c40e9a59b2c91265d5e64e52641bedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9ub3RlZ3B0LmlvL2FpLWhvbWV3b3JrLWhlbHBlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03bf345db03ef71ec90aa2aadf88d789d35a6ea1739fc477e8d8e600ccb74775JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9tZXdvcms&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c7ea1cd4e4f27737cf3bfe23ccf9936b609e7c3ca2a125dbb1f43abb1a88e37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9zdHVkeXguYWkvYWktaG9tZXdvcmstaGVscGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e32ceb5e283353cc7eb79623bc975556625cfd7dac55edeb2282b0d4df345888JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9jbGFzc3Jvb20uZ29vZ2xlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc201d39b78796784abf0d86dc6a2612545f8632c8743ee6b3592837d482bbb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly93d3cuZ2F1dGhtYXRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6c6fb48313c3e5beb569f98009d515673aa702bef83b0856e3f661c48395fdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly93d3cuaXhsLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd884b68a25c65d3f77d432ea5388142242fdf7c5952b524279aae0d3eb76ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9haS10dXRvci5haS9ob21ld29ya2lmeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=364b63f370d3198ca6fc3f3ad58cd8e3d1870c666b5c28c18303c781c9fc7320JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9icmFpbmx5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3cd90df80e4381febe15adbc61b996ba2d02a9f226905d58bb771c3c52bd603JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9lZHVicmFpbi5haS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=792cd11354347ac58f18c13678ab5e26e9d1b48728a050f0578996ebcb749130JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11278d61-fa76-6d68-3340-9a83fbd16cfe&amp;u=a1aHR0cHM6Ly9ob21ld29ya2FpLmlvLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55923817dbf780d3c861b9f8b1b316dd36e98296fa1a3bb3e6085788729ea50cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL2NoYXJhY3RlcmlzdGljcy1nb29kLWxlYWRlci8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d66619fc5dc0f60aed55de6523d0e1570c52e5eeb9511b730b38f96bbb8cdc4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGVhZGVyc2hpcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e276bedf43abc629f3399f7022ebfd76372a7c6450690955e7e3c8a1990dd9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cubWNraW5zZXkuY29tL2ZlYXR1cmVkLWluc2lnaHRzL21ja2luc2V5LWV4cGxhaW5lcnMvd2hhdC1pcy1sZWFkZXJzaGlw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0cb6c8c06f1a6cd19ea25ae12feb98e9be0b9b7590a7a9b07a1f83b4e8edca1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly9lbWVyaXR1cy5vcmcvaW4vbGVhcm4vd2hhdC1pcy1sZWFkZXJzaGlwLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5dd7316ca688cd97e70295ff6e67ac0593423254f81af4d5ee109936db117228JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL3doYXQtaXMtbGVhZGVyc2hpcC1hLWRlZmluaXRpb24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ec21c50821bd8901dca4577c2fd5a52b0a6819b42e299466b9aa52c7451a722JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvbGVhZGVyc2hpcD9tc29ja2lkPTNlNmM3NzIzZjg0MjY5ZTYzYjY0NjBjMWY5MDE2OGZl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3a65fb21011dcf08a4899240096a77bdb4fbc04c5f52b5ad91bb4ecb8bea469JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cuaW1kLm9yZy9ibG9nL2xlYWRlcnNoaXAvd2hhdC1pcy1sZWFkZXJzaGlwLWhvdy1pcy1pdC1ldm9sdmluZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d18486a3903794fa94e9b0121b1c494bc9f8d2742d57a2f5b6d6e7673db11ab8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly9wcm9mZXNzaW9uYWwuZGNlLmhhcnZhcmQuZWR1L2Jsb2cvaG93LXRvLWRldGVybWluZS13aGF0LW15LWxlYWRlcnNoaXAtc3R5bGUtaXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0929803e11db6d106c2894b283b85f06fa7f6de16735b1013920361ce602a513JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly93d3cubWFuYWdlbWVudHN0dWR5Z3VpZGUuY29tL2xlYWRlcnNoaXBfYmFzaWNzLmh0bQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3841ad915bfc01426c11ee45d48ca7fd193ecc9b4501baf83f39601315ff79b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e6c7723-f842-69e6-3b64-60c1f90168fe&amp;u=a1aHR0cHM6Ly9scHNvbmxpbmUuc2FzLnVwZW5uLmVkdS9mZWF0dXJlcy9wc3ljaG9sb2d5LWxlYWRlcnNoaXAtd2hhdC1tYWtlcy1ncmVhdC1sZWFkZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2113a9d270bc64292a62d2a92106cc801b138365f678c8b97fed48be673a9198JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudG9yc2hpcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33ce944e47344c922c448002547320f94ded1c6b1544d5f7d1ccbfbae59f2ed1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly9wb3NpdGl2ZXBzeWNob2xvZ3kuY29tL21lbnRvcmluZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=084e57526c0a9eb251410f27d5dc912e876e8a69a705973e49a8bbbb6efb8807JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuY2ZhaW5zdGl0dXRlLm9yZy9pbnNpZ2h0cy9hcnRpY2xlcy9tZW50b3JpbmctMTAxLWd1aWRl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08715d54dc27b95254c9f9392d63b959ec8ea48b35f9a2f27367bf3608b8cd09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuaW5kZWVkLmNvbS9jYXJlZXItYWR2aWNlL2NhcmVlci1kZXZlbG9wbWVudC93aHktaXMtYS1tZW50b3ItaW1wb3J0YW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c7d893ba28db4e5598d14cebf028b5a8a3ecb2cf756c8d38fe4aa5bd89050b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuYXBhLm9yZy9lZHVjYXRpb24tY2FyZWVyL2dyYWQvbWVudG9yaW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e691bc4a7d938d75cbe2474c17fea6c59930e480210741bba8afc7c582cf838fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZW9mcGVvcGxlLmNvbS9ncmVhdC1tZW50b3Iv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45b258cb38a7431a1c2341aa8474d9f7c7f7f7d7a27aa6fc24dbbc89da8db5ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuaGFydmFyZC5lZHUvaW4tZm9jdXMvbWVudG9yc2hpcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04b83d4de92f44426b329458fea1f887ffc78e331b1f8a9516404253cd8f53b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9ibG9nL3RoZS1wZWFrLWV4cGVyaWVuY2UvMjAyNjA0L3doeS1tZW50b3JpbmctbWF0dGVycz9tc29ja2lkPTAxM2E2MjAyMzNjNzYyODAyZmVjNzVlMDMyNmQ2M2E0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1220a74269180ffca3ec678dc8a34d92d6a80bc7e5238748d710b72b06f3b0efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRvcnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d0fe3a26af1bdf9b14ec91c82f260b0afafb07eff2e7a6bb0c815bc7ad53848JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=013a6202-33c7-6280-2fec-75e0326d63a4&amp;u=a1aHR0cHM6Ly93d3cuYmJicy5vcmcvYS1mdXR1cmUtYnVpbHQtb24tbWVudG9yc2hpcC13aHktbWVudG9yaW5nLWlzLXRoZS1lc3NlbnRpYWwtaW5mcmFzdHJ1Y3R1cmUtb3VyLWZ1dHVyZS1uZWVkcy1ub3cv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d892ab5a03b381c12e482360908120327ba7ff202e6b611cd6e26b64c6fa075cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9hcnRpY2xlLnBpbnBvaW50aHEuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24f91df5693aa46f3ff924b35b5e0d6d41a67174a368f60aeb261b304a68f099JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9hcnRpY2xlLnBpbnBvaW50aHEuY29tL2VuL2pvYnMvNTgzNDc4L2hpcmluZy1wcm9jZXNz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3afbe6745e44eeb189b60598c07a8a70c144082aafe95cd9006eef1cc5d8644JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9kb2ZlLnBpbnBvaW50aHEuY29tL2VuL3Bvc3RpbmdzLzk1MTc0YTNjLTAwNmItNDFlZS04MGFhLTE4Nzg5ODM1ZTU4OQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c398e39f7f20e8438cad1ea436b6886674caf65f6289b4d74e621b3e790169dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9jb2Zvcm1hLnBpbnBvaW50aHEuY29tL2VuL3Bvc3RpbmdzLzUwOGU5MDUxLWEwNWEtNDFiMy1iYTBlLTExNTZmMDQwYWEyMg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11ae73e9cb07614a8e251626a5fb7de7d2ccd1720284d078dcffa6158482e618JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9ueXBsLnBpbnBvaW50aHEuY29tL3Bvc3RpbmdzLzc3MjMxZWQwLWM4YWEtNGVkNS1hNDllLTM3MjczMjRkNWJhNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df45b1560daf8304245e3247710eebc9fb743ab702c94969b2a7e9fa0a3b5948JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9hc3Ryb2xhYi5waW5wb2ludGhxLmNvbS9wb3N0aW5ncy84NDY3Zjg3NS1lMzdjLTQ3OWQtOGI3Ny05N2I3OWZmNTRmMjM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2234a3db00cdf95ae9d4a5d114f5608cfc8d0d33286356d599980f3da91be21fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9oYXJwZXJjb2xsaW5zLnBpbnBvaW50aHEuY29tL2NhcmVlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99a7024ec6953632deee80f9dfe4afad8f1b1c7827e8314f2dcc015348909a13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly93d3cucGlucG9pbnRocS5jb20vcGlucG9pbnQtYWk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af63fd2eba9ab8a77322cd8a7b6dbc7ce7961db4ef50901fa3342bf81d112d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly9hc3Ryb2xhYi5waW5wb2ludGhxLmNvbS9lbi9wb3N0aW5ncy80NDIwNmExNy0wMjE0LTQ5YzQtYjE3Ny04ZjQ4MzNkYjcyNmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efd77d0ca829d6a7b05abb7e08f4e5cf11f43210e98d012fbfa44b267da46ef6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36d1c1f3-8ac2-6a8c-2218-d6118bb36bca&amp;u=a1aHR0cHM6Ly93d3cucGlucG9pbnRocS5jb20vYWktYXBwbGljYW50LXRyYWNraW5nLXN5c3RlbQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e802bd30f8006190c326f153989e198269db29f813b54a2d0cdea2994f4cb918JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS8_bXNvY2tpZD0zNmU5MjkxN2MwNDY2OGMwMDhhYjNlZjVjMWVhNjk3NA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49e3e4c0d762f166c3100ab9a164f8d7befcedb318abf1cce5e077106614c099JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3c87ef532549e129614822b6b51e1e0b3ccc13aa476891249fa4ffc0a5d65d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRWR1Y2F0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eeafa33cc6f5f258c5e8c6affc5d7c2f0777ca5c3d231d7815a5b5e7c4b16eb0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZWR1Y2F0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=574f090bc6399d8e3e2d70d412f02fb88259760a8065e62c63031187e362764fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96ca9147487a4b0b1f045b73d97bb87b588d10681da16a220e18ba0c061e118bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cuZWQuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb6a2fd287ee42b6c1abb97b1de9ee09ddac0479a215fbcf1857b58763a68839JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85cbd87ae792011fb999da8c6bcfaf8867e4505d14a75806100cbe66b5e474cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=297969f5a82827129134a85dfd674bf604a8c652c0d4a08c7fb6663a0f1d1646JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df5dad362276dfc1e18c79c600651b4a1889330233300d546585af1cf81cee77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36e92917-c046-68c0-08ab-3ef5c1ea6974&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS9yZXNvdXJjZXMvZ2FtZXMvP21zb2NraWQ9MzZlOTI5MTdjMDQ2NjhjMDA4YWIzZWY1YzFlYTY5NzQ&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=096191a1aed14e465fb5e6696b56ba50f930f61db8c3ad46bf6ccb54d4803475JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4f4cfc8c5f8a2c6012be706fb5ef4f82990e79cfc81b47098a22521e418a3ceJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b179781b3d7a86a32ae2a3ba8e5292884df78d680d86ac0352edfb7b56ee4803JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1Yd3VETVNsRXJraw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99de92ec15970e4956d0c77ea5bdbb133e71a48b90ebd9c808b4c10d9cc958feJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjg0MDAzL3lvdXRoLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6384463917b03433202ef20ab8029d5d669f81cb9973534762438e36647920fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=287ad8016b1302fadf19498bfdbdb206b7259d5ad328d9f14aa60f829a50e8daJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04f76d9ad927e6c49ace2a81a858f027fd0a5e52f8f18e0955d0a4f23ca8d940JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3lvdXRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caca9a5bbcd94300c784abac0a98e8ab09cc1cb2a75bd7e70378113dd91ef056JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly9kZWNpZGVyLmNvbS8yMDI2LzA5LzIwL3lvdXRoLXNoYXJvbi1ob3JnYW4taGJvLXJldmlldy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=919795d1074a1c3faef70ad5c6143fe060fbd02f0b59304a78bc55bdbf565292JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly93d3cudHZpbnNpZGVyLmNvbS8xMjkzMTk2L3lvdXRoLXNlYXNvbi0yLXByZW1pZXJlLWRhdGUtdHJhaWxlci1jYXN0LXBsb3Qv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0c7c3689de5a3721ae12c14044593dbfcd4bd45798946b85cdab3a0d31a9840JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cf2e0fc-9bfc-6ed8-08a0-f71e9a716f4d&amp;u=a1aHR0cHM6Ly95b3V0aC5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=719abb7c01d9edc77d2631dfd47e44d2f9a89750f0d5da1e1120ba842fd78368JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly9zdGxjYy5lZHUvdHV0b3Jpbmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76a17fe46b498dbb8c4275e7a5a5185eaebedd5ad846505139cadad00c10e730JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly93d3cudHV0b3IuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5e7ce8cf2e3e6131b9e4fdb9cc97ca1438e2359ea901d556f7c3ddd74a77f39JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly93d3cudmFyc2l0eXR1dG9ycy5jb20vdC9taXNzb3VyaS9zdC1sb3Vpcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce7d47f99354fd0920b8e41d995a21b633f2347918a322b09afdde1ba0fcc17bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwcm9mLmNvbS9sZXNzb25zL2FsbC10dXRvcnMvc3QtbG91aXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ada9bfe5c60ec9fca3a22d447e5e0adf1912451153ebd310194e9bfb5b04bdf7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly93d3cuc2xjbC5vcmcvY2hpbGRyZW4tZmFtaWxpZXMvb25saW5lLXR1dG9yaW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d143493bb5fdaf1a481b29ccfb018c81a86b06ac8f9fd9e8f56eadcb4b18fc17JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly9jbHVienR1dG9yaW5nLmNvbS9zYWludC1sb3Vpcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74d37d4415dcc0a75a6116fc704081f3b26dc6c7fa6ee52ecb635045d539af9bJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly90dXRvcmluZy5rMTIuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8af0478e660c27b17ff2b002e42b43fd964f8986f00cb165417d6d4bf9432b5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly93d3cuaW5kZWVkLmNvbS9xLVR1dG9yaW5nLWwtU3QuLUxvdWlzLC1NTy1qb2JzLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea2a5e7f66adda23986278fc8a02d598627adf94564e02b33aa7b5b424dd7b3fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cHM6Ly9leWNhY2FkZW15c3RsLm9yZy90dXRvcmluZy1zdC1sb3Vpcy1tby8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4263f13da6af95ecf8a06c0a9515e5163da1067532294ffc993a4b22604d3e95JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b42e3a3-b707-610e-0537-f441b6da6095&amp;u=a1aHR0cDovL3d3dy5kYXJydHV0b3JpbmcuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbe0291708d16966b7e1a69ad32d85f6193409f19c0f1a5fb5ab84843fd5bfb9JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfKGZpbG1fc2VyaWVzKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6c980d3c7bc6e37d4798ac43bcb23611116f481f33d9ce1789e43094d4f2cb1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9hZnRlci0yMDE5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9de62bd83d3e2f317bf8ed64659c6bcc959d943c0ee90296c454286455b320ffJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly9tb3ZpZXdlYi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1dff28f8e0fa1ea0602ce39d60b192426b9080b20f2093cab4638607789b04cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ0MTI2NDc2L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25c73a4291b5588891edbe7b2cfb34c5e582b3f9d3042153efadf4d1000647ebJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfJTI4MjAxOV9maWxtJTI5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e919db038f7ba106e063ec04d54ad90a93146ef7a251f4283f1188c26e32afaeJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODAyNDQzMTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=478c20d2badbf57ec8c924805e2ecfad110e8a2b3158e904589e8ed77f73e0a2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L3doZXJlLXRvLXdhdGNoLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a9c34caa1a5b984220ba4dca7e551fe1b6c6b2464277fd8ab049bb46092df5fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly92aW1lby5jb20vMzM2ODUxNTI2P21zb2NraWQ9Mjk1YmVlYzExOTMxNjgxNDIxMjRmOTIzMThlYTY5NDI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ddc39b2a107ec3def59e9a87d724166973783188725d3029ceb7e7ce56225f21JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly9maWN0aW9uaG9yaXpvbi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3de93b9a0a9d4e1f0500ff6e3f3fca6cee6829c4a27f0062d0fb5b1746e3616JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295beec1-1931-6814-2124-f92318ea6942&amp;u=a1aHR0cHM6Ly9tb3ZpZXNhbnl3aGVyZS5jb20vbW92aWUvYWZ0ZXItMjAxOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=418772bec35ea4979b85da11952841a992bc3ea9d6773193ac467f7d788869fcJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1bd1d7019467c84714cfbc9275f832d331515b34847ac241d3a024bc239c378JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18f48237eee49961cde2749d09bead104eb4ffd674661add0f8004c7bb8b67b5JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2xpdGVyYWN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef4c1d04c1b75cc1d43b96f521569224ed04d936c1b877392947f84301ab8c09JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeS9uZWVkLWtub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4c976af395f1d12d1fc06c735fca3e95d972c422a6f9365ee8ee2548dc0e255JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cudGhlZ2xvYmFsc3RhdGlzdGljcy5jb20vbGl0ZXJhY3ktcmF0ZS1pbi10aGUtdW5pdGVkLXN0YXRlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00f5f38f6c4b2f5b1b9a2a515ead84686bb361dda93673f22ee4f3026fee53c9JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2xpdGVyYWN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02742c89e9c6c366d8747dbb1ce0a5193a512e92a91abb0770703a205e8a6e9aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9xdWVyeS1saXN0L2wvbGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e23fa25b43559e48c69c6bc9dc84cd57a86ef0a785288b70bee5eb51a13d23aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly9vdXJ3b3JsZGluZGF0YS5vcmcvbGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=018cfaf0562bad7c959893f9bfdc002e747f4783f99c65bc6a3e712c865df2dbJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly9uZXdzLmhhcnZhcmQuZWR1L2dhemV0dGUvc3RvcnkvMjAyNS8wOS93aGF0cy1kcml2aW5nLWRlY2xpbmUtaW4tdS1zLWxpdGVyYWN5LXJhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93f82b3b44de8a790661cb894efdf89231c97bdbe40d11e97cc931e3eba0fc5cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b9c8b50-a993-60fa-2aaa-9cb2a83761f4&amp;u=a1aHR0cHM6Ly93d3cubGFuZ3VhZ2VodW1hbml0aWVzLm9yZy93aGF0LWlzLWxpdGVyYWN5Lmh0bQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9bea3cbeba25246c8f99a7ed418479c5aff87e4b796a6438713bd72eb5965a17JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9ub3RlZ3B0LmlvL2FpLWhvbWV3b3JrLWhlbHBlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02fe643d9542ea8c3640d342088c150939f3c7f385ff9b03f8af73895baae79dJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9tZXdvcms&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d8063d847cadf7a2d41bf9bb0ad2dadfd0046238dcdd619288cc5e8a48dc289JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9jbGFzc3Jvb20uZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9b1cc3a90c5d9160fbd2379ab621994aadbc68192c3bb840179cf311756bce7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly93d3cuZ2F1dGhtYXRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ed9e890c59d77a23e111957caab24a0ab3684472b9ece6863f0b81d011270cdJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9zdHVkeXguYWkvYWktaG9tZXdvcmstaGVscGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=272bde7b1cb8fcdb32d43f446d8b65dfe6db1313a71e733b87d21012f517fce2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly93d3cuaXhsLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9aad8a9417659d2fde304bf74ff649df4257623aafc61a06f46d1dbd09e07313JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9ob21ld29ya2FpLmlvLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c166e868c31a6f74f599f1bee444eeae03118ab34ed0751e686acf3e0bd8e7fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9ob21ld29ya28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d02403b32475e556962ba63688f9be93826401c8ade4782fa3d44088237f69eaJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9haS10dXRvci5haS9ob21ld29ya2lmeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02148091920b263aea263efd2855c98ded486710b8d62e535a9b09e57c074e0cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39a42a49-8e99-60d9-17f8-3dab8f7461fb&amp;u=a1aHR0cHM6Ly9lZHVicmFpbi5haS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c2f99387d46277439a183d79921c7c996339e24c7916889bbd5360a84b75a76JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL2NoYXJhY3RlcmlzdGljcy1nb29kLWxlYWRlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efb2f498720988c78be3def42b65a8d3f52c349a5bbf1bf88f8aed0fc8fd834cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGVhZGVyc2hpcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06233b0a0fe5be707fba6cb1eb4bd9f43f3ba1356952f9605e18428ad97522ebJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cubWNraW5zZXkuY29tL2ZlYXR1cmVkLWluc2lnaHRzL21ja2luc2V5LWV4cGxhaW5lcnMvd2hhdC1pcy1sZWFkZXJzaGlw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6135d1acfd7aca53cdfd390df74ff083b2ab4449c02c8b66c711686d39ea4edbJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly9lbWVyaXR1cy5vcmcvaW4vbGVhcm4vd2hhdC1pcy1sZWFkZXJzaGlwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2f00653810dfb5a951ac9cb365b4244ac95b82fe831cc713731fef1fa773469JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL3doYXQtaXMtbGVhZGVyc2hpcC1hLWRlZmluaXRpb24v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b62ca300cd7b8108523e69c624d3b1d0eb5ad2258a0eddedb4ee709968661b0JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvbGVhZGVyc2hpcD9tc29ja2lkPTNjOTIxNjFhNmVkMzY3ZGIxYjM3MDFmODZmYTg2NjE4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88561466636b544b2c232f835bb0486d49fe0b6fc8a2253bed980c4cd01afb2fJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cuaW1kLm9yZy9ibG9nL2xlYWRlcnNoaXAvd2hhdC1pcy1sZWFkZXJzaGlwLWhvdy1pcy1pdC1ldm9sdmluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9331dd20efc28a914aa101b2c51c7532d0d973bb8ab84edf819a95c3fb740f58JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly9wcm9mZXNzaW9uYWwuZGNlLmhhcnZhcmQuZWR1L2Jsb2cvaG93LXRvLWRldGVybWluZS13aGF0LW15LWxlYWRlcnNoaXAtc3R5bGUtaXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3f15255f681f588976d5be16100035290b7eb976b23e40e73bb48492d5f6c19JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly93d3cubWFuYWdlbWVudHN0dWR5Z3VpZGUuY29tL2xlYWRlcnNoaXBfYmFzaWNzLmh0bQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=259f4f180f26f6050518eb96ee3d41f9c8d777d582c910bd10229ae4ff9144c4JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c92161a-6ed3-67db-1b37-01f86fa86618&amp;u=a1aHR0cHM6Ly9scHNvbmxpbmUuc2FzLnVwZW5uLmVkdS9mZWF0dXJlcy9wc3ljaG9sb2d5LWxlYWRlcnNoaXAtd2hhdC1tYWtlcy1ncmVhdC1sZWFkZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=074111df215f3aa95bb98b3c5e0909b91402755e9cd119800df48ee278207bf7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudG9yc2hpcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b60c86cd01c94f2dfd0c35298c780422fd6697b162a4d7527b502bfbccaa7e7JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly9wb3NpdGl2ZXBzeWNob2xvZ3kuY29tL21lbnRvcmluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6bfa0b8811e7c4e6b5d82f5efebce8568a597ab5f0e9f991c1c5ee7200410aaJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuY2ZhaW5zdGl0dXRlLm9yZy9pbnNpZ2h0cy9hcnRpY2xlcy9tZW50b3JpbmctMTAxLWd1aWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48795c2591055c51cb6ea68372bc4ad17d42ff6dd668dd72984645a3c8340b06JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuaW5kZWVkLmNvbS9jYXJlZXItYWR2aWNlL2NhcmVlci1kZXZlbG9wbWVudC93aHktaXMtYS1tZW50b3ItaW1wb3J0YW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3994b508ce5c4a50ea91d0a182cdf91bc5ed2f85f2ec3b0e302efdb7b621d0f2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuYXBhLm9yZy9lZHVjYXRpb24tY2FyZWVyL2dyYWQvbWVudG9yaW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d42c87f88af2fc39952045d2555ad30fbb378a6249e114bee6eec56a71ee7341JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZW9mcGVvcGxlLmNvbS9ncmVhdC1tZW50b3Iv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=216770fc7349b3a2b92cc2b6d039e3f57894fea6f63c4aefad379de9948dd975JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuaGFydmFyZC5lZHUvaW4tZm9jdXMvbWVudG9yc2hpcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdeb3337455503300fc552a921fb21debaeb8b55cacc8908880deac35fe9dd64JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9ibG9nL3RoZS1wZWFrLWV4cGVyaWVuY2UvMjAyNjA0L3doeS1tZW50b3JpbmctbWF0dGVycz9tc29ja2lkPTM4MzAxYjYyNGUzZTYxMjMxNDYxMGM4MDRmN2I2MDkx&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d98d61f7a3e3d9a94cf027a12715991c8ee64ca9d93519c9321f51e681f37f85JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRvcnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb818d7b5468a439b518c2e826a9279e4eedcbf8c04b3c7aebf71106297f75c2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38301b62-4e3e-6123-1461-0c804f7b6091&amp;u=a1aHR0cHM6Ly93d3cuYmJicy5vcmcvYS1mdXR1cmUtYnVpbHQtb24tbWVudG9yc2hpcC13aHktbWVudG9yaW5nLWlzLXRoZS1lc3NlbnRpYWwtaW5mcmFzdHJ1Y3R1cmUtb3VyLWZ1dHVyZS1uZWVkcy1ub3cv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4599cac79afb78401c466de01473b9dc34f1369ec6862dfee12f08ec6c497c41JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1205d3ab08decf420495efa30f04b721c95998862f6c1f9a2c4fe5f56129c7d3JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly9yZWFkaW5nZWdncy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ac619b3012621ad01ea680490e48823b671c523fd2e6d127491c6b352a9f776JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ2Etei5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18cbfdf6649ef93148382b4b636050d742435fe9aa714a46b14c51777bec6b9dJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9SZWFkaW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f846c8e2d26415544c15cc2cfa72764ffe34f3b7bef105a78cbb428d26055d7aJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9SZWFkaW5nLF9CZXJrc2hpcmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df3d9bea707aca12071f95a63d4457118fe8b9a31476bce8dd0b7fe2d780cbb1JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ3JvY2tldHMub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ebda6c21d3f848eb068d013b3d01c412f5ce341c31a192246b742bc4df2a2e4JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3JlYWRpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b8f746944639c685054c78992433b0e12ee49aedc84ffc1e89ec13e3edbf2c2JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ3JvY2tldHMub3JnL3RvcGljcy9hYm91dC1yZWFkaW5nL2FydGljbGVzL3doYXQtcmVhZGluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75069b93ef174a0f545b457c167c93478523545a2a2a89dfc154d26f2bf82e2eJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly9zY2llbmNlaW5zaWdodHMub3JnL3doeS1yZWFkaW5nLW1hdHRlcnMtd2hhdC1uZXVyb3NjaWVuY2UtcmV2ZWFscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a81f75f2aacc1b146c7130cd951f2c2e3c25ec04f5ed44fc192c15ac4f06c80JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05d18060-0ba7-67d5-1007-97820ab2664a&amp;u=a1aHR0cHM6Ly9sZWFybmVuZ2xpc2guYnJpdGlzaGNvdW5jaWwub3JnL2ZyZWUtcmVzb3VyY2VzL3JlYWRpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f393a8e3ef3f2fd165f67160ca6ede8a1447c47c8e8d6fbc0f48bab25bcac5edJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS8_bXNvY2tpZD0zNDg0YTI3YzkwMjI2M2NjMzU5MGI1OWU5MTRhNjJlMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e43431ef74d7f5ac8c135f8f8965ee76116e1c5fdb2efdc967312c55b564a1cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRWR1Y2F0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81dd628466d589ae1daf27778792e1b7aee6cf1222e716c598ff6d0718bee7d0JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cuZWQuZ292Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52e3a5b1ea8165e4c61474dbaf274f571cf445b774aa2350719d80c150678e4cJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VkdWNhdGlvbmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d64004ff1963d41c842539423e0e8c108f304cd28faccb79eda4b49b1f9ecf94JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZWR1Y2F0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e4d578fec6adfee2c13e313ce7dc1cc3e4dfec8d8e5656ba9c0ca4dc85d3953JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VkdWNhdGlvbmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e63b19fb59216d50b08e90ede0c7535a252027476c804491f2cc26b2bac2a50JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VkdWNhdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539570a7b712ba3e0ba5464fa67bb708da78e6e9e4f94a7e5d8a6eda529287ecJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS9yZXNvdXJjZXMvP21zb2NraWQ9MzQ4NGEyN2M5MDIyNjNjYzM1OTBiNTllOTE0YTYyZTM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf79fcb6ab9bdc81b90b699fff294806fee49c063d9075d7e4c6e2e6e7b347bdJmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS9lbi9lZHVjYXRpb25hbD9tc29ja2lkPTM0ODRhMjdjOTAyMjYzY2MzNTkwYjU5ZTkxNGE2MmUz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d303ea4204655c57bbea617d607a8873c0185684eb65aecd7d5284a1666eb76JmltdHM9MTc5MDU1MzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3484a27c-9022-63cc-3590-b59e914a62e3&amp;u=a1aHR0cHM6Ly93d3cuZWR1dG9waWEub3JnLw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Youth_and_Tutoring.xlsx
+++ b/results/scraped_Cape_Town_Youth_and_Tutoring.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="453">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,21 +40,18 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Youth(TV Series 2026– ) - IMDb</t>
-  </si>
-  <si>
     <t>Youth| Official Trailer | Ken Karunas, Devadarshini Chetan, Suraj ...</t>
   </si>
   <si>
     <t>Youth(2026) - IMDb</t>
   </si>
   <si>
+    <t>Mutta Kalakki Music Video |Youth| Ken Karunaas | Suraj …</t>
+  </si>
+  <si>
     <t>Youth-Wikipedia</t>
   </si>
   <si>
-    <t>Mutta Kalakki Music Video |Youth| Ken Karunaas | Suraj …</t>
-  </si>
-  <si>
     <t>Youth(2026 film) - Wikipedia</t>
   </si>
   <si>
@@ -67,37 +64,40 @@
     <t>YouthHub - EmpoweringYouthfor Jobs, Skills &amp; Opportunities</t>
   </si>
   <si>
+    <t>WatchYouth| Netflix</t>
+  </si>
+  <si>
     <t>Introduction 1.1Youthis the most energetic and productive section of ...</t>
   </si>
   <si>
-    <t>How to get help in Windows - Microsoft Support</t>
-  </si>
-  <si>
-    <t>About Get Help | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Windows 11 Forum</t>
-  </si>
-  <si>
-    <t>Enable or Disable Tips and Suggestions Notifications in Windows 11</t>
-  </si>
-  <si>
-    <t>ヘルプについて | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Informationen zu Hilfe | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Como obter ajuda no Windows - Suporte da Microsoft</t>
-  </si>
-  <si>
-    <t>Aide et apprentissage Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>關於 [取得說明] | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Ausführen von Problembehandlungen in „Hilfe abrufen“</t>
+    <t>Hear Ye Hear Ye looke at ye olde porn - XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>Real incest stories | XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>Family Trip to the Nudist Camp - part 4 - mom and sister, dad</t>
+  </si>
+  <si>
+    <t>Gabe | Page 5 | XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>chinese porn - XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>Porn Comix | Page 75 | XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>Japanese Incest Porn. - XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>MISHELL`S VINTAGE PORN. | Page 14 | XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>who is your favorite porn star? | XNXX Adult Forum</t>
+  </si>
+  <si>
+    <t>Fucking Gifs | XNXX Adult Forum</t>
   </si>
   <si>
     <t>After(film series) -Wikipedia</t>
@@ -160,15 +160,378 @@
     <t>The Importance ofLiteracy</t>
   </si>
   <si>
+    <t>Your AdSense for YouTube account was deactivated</t>
+  </si>
+  <si>
+    <t>YouTube TV Help</t>
+  </si>
+  <si>
+    <t>如何在中国大陆用「合法」的方式观看到youtube上面的「有价值」的 …</t>
+  </si>
+  <si>
+    <t>YouTube公司 - 知乎</t>
+  </si>
+  <si>
+    <t>YouTube-video's uploaden - Computer - YouTube Help - Google Help</t>
+  </si>
+  <si>
+    <t>Opret en YouTube-kanal - Hjælp til YouTube</t>
+  </si>
+  <si>
+    <t>YouTube ความช่วยเหลือ</t>
+  </si>
+  <si>
+    <t>YouTube Ajutor</t>
+  </si>
+  <si>
+    <t>YouTube Trợ giúp</t>
+  </si>
+  <si>
+    <t>Не удается зайти на YouTube</t>
+  </si>
+  <si>
+    <t>What isLeadership? Definition, Meaning &amp; Importance</t>
+  </si>
+  <si>
+    <t>The 12 Characteristics of a Good Leader | CCL</t>
+  </si>
+  <si>
+    <t>Leadership-Wikipedia</t>
+  </si>
+  <si>
+    <t>Leadership: Meaning, Characteristics, Theories and Styles</t>
+  </si>
+  <si>
+    <t>What isleadership: A definition and way forward | McKinsey</t>
+  </si>
+  <si>
+    <t>What IsLeadership? A Definition Based on Research | CCL</t>
+  </si>
+  <si>
+    <t>What IsLeadership? Definition, Types, and Skills - Naukri.com</t>
+  </si>
+  <si>
+    <t>What IsLeadership? -Mind Tools</t>
+  </si>
+  <si>
+    <t>Leadership-Psychology Today</t>
+  </si>
+  <si>
+    <t>What IsLeadership? Meaning, Definitions, Theories, Styles ...</t>
+  </si>
+  <si>
+    <t>7 Days to Die Mods: Safe, curated 7D2Dmoddownloads</t>
+  </si>
+  <si>
+    <t>7 Days To Die Mods</t>
+  </si>
+  <si>
+    <t>Discover -7 Days to Die Mods</t>
+  </si>
+  <si>
+    <t>7 Days to Die Mods- CurseForge</t>
+  </si>
+  <si>
+    <t>7 Days To Diecollections -Nexus Mods</t>
+  </si>
+  <si>
+    <t>All Weapon and ArmorMods-7 Days to Die</t>
+  </si>
+  <si>
+    <t>7 Days to Die Mods| The Fun Pimps</t>
+  </si>
+  <si>
+    <t>7 Days to Die Mods(194) | 7DTDMODLab</t>
+  </si>
+  <si>
+    <t>7D2DModLauncher — V5</t>
+  </si>
+  <si>
+    <t>Practise Englishreadingskills | LearnEnglish</t>
+  </si>
+  <si>
+    <t>Teach Your Child To Read Early, Step by Step |Reading.com</t>
+  </si>
+  <si>
+    <t>Reading-Wikipedia</t>
+  </si>
+  <si>
+    <t>English Reading| Learn English</t>
+  </si>
+  <si>
+    <t>BBC Learning English - TheReadingRoom</t>
+  </si>
+  <si>
+    <t>Reading- Test-English</t>
+  </si>
+  <si>
+    <t>EnglishReading:English Texts for Beginners- Lingua.com</t>
+  </si>
+  <si>
+    <t>Free Online IELTSReadingPractice Test &amp; Solution Collection</t>
+  </si>
+  <si>
+    <t>Welcome to Open Library | Open Library</t>
+  </si>
+  <si>
+    <t>Reading A-Z: The onlinereadingprogram with downloadable books to ...</t>
+  </si>
+  <si>
+    <t>Education-Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | Ministry of Education</t>
+  </si>
+  <si>
+    <t>EDUCATIONALDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Education.com | #1EducationalSite for Pre-K to 8th Grade</t>
+  </si>
+  <si>
+    <t>EDUCATIONAL| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Educational Games- Play Online for Free! - Poki</t>
+  </si>
+  <si>
+    <t>EducationWorld - India's most credible school rankings Since 1999</t>
+  </si>
+  <si>
+    <t>Definition, Development, History, Types, &amp; Facts - Britannica</t>
+  </si>
+  <si>
+    <t>EducationalQualification: Meaning &amp; How to Write It</t>
+  </si>
+  <si>
+    <t>Education vs.Educational— What’s the Difference?</t>
+  </si>
+  <si>
+    <t>ChatGPT: Chat, Work, Create &amp; Code with AI</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>IntroducingChatGPT- OpenAI</t>
+  </si>
+  <si>
+    <t>OpenAI | Research &amp; Deployment</t>
+  </si>
+  <si>
+    <t>ChatGPT-Wikipedia</t>
+  </si>
+  <si>
+    <t>Get started |ChatGPT</t>
+  </si>
+  <si>
+    <t>ChatGPTPlan | Free</t>
+  </si>
+  <si>
+    <t>DownloadChatGPT</t>
+  </si>
+  <si>
+    <t>GPT-4 | OpenAI</t>
+  </si>
+  <si>
+    <t>ChatGPT MD - GitHub</t>
+  </si>
+  <si>
+    <t>ChatGPT Chat Exporter - GitHub</t>
+  </si>
+  <si>
+    <t>ChatGPT - 知乎</t>
+  </si>
+  <si>
+    <t>ChatGPT - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPTPromptGenius - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPT 有哪些神奇的使用方式？ - 知乎</t>
+  </si>
+  <si>
+    <t>GitHub Pages documentation - GitHub Docs</t>
+  </si>
+  <si>
+    <t>Download GitHub Desktop</t>
+  </si>
+  <si>
+    <t>Codex with ChatGPT - GitHub</t>
+  </si>
+  <si>
+    <t>chatgpt · GitHub Topics · GitHub</t>
+  </si>
+  <si>
+    <t>Virgo &amp; Gemini: Love Compatibility | Astrology Answers</t>
+  </si>
+  <si>
+    <t>怎么看谷歌发布了 Gemini 3.6 flash和 3.5 lite，但是 pro 又缺席？</t>
+  </si>
+  <si>
+    <t>Gemini Zodiac Sign - Astrology Answers</t>
+  </si>
+  <si>
+    <t>Gemini的模型是不是已经快被淘汰了？ - 知乎</t>
+  </si>
+  <si>
+    <t>《记忆革命：Gemini 1.5如何让Transformer突破百万级上下文枷锁》</t>
+  </si>
+  <si>
+    <t>Gemini Love Horoscope - Astrology Answers</t>
+  </si>
+  <si>
+    <t>Gemini Weekly Horoscope - Astrology Answers</t>
+  </si>
+  <si>
+    <t>Gemini Woman: Traits, Love, &amp; More - Astrology Answers</t>
+  </si>
+  <si>
+    <t>如何评价Google DeepMind的Gemini 3.8 Flash模型？</t>
+  </si>
+  <si>
+    <t>Gemini 3.5 Flash 正式发布，你怎么评价这款模型? - 知乎</t>
+  </si>
+  <si>
+    <t>Aan de slag met livestreamen - YouTube Help - Google Help</t>
+  </si>
+  <si>
+    <t>创建 YouTube 频道 - YouTube帮助</t>
+  </si>
+  <si>
+    <t>Convert to PDF context menu in explorer missing</t>
+  </si>
+  <si>
+    <t>Word file Redline not showing when converted to PDF</t>
+  </si>
+  <si>
+    <t>How to convert PDF to image? - Ask Ubuntu</t>
+  </si>
+  <si>
+    <t>PDF to word conversion software? - Ask Ubuntu</t>
+  </si>
+  <si>
+    <t>Unable to convert a PDF into Word as it just say "Uploading" || Adobe ...</t>
+  </si>
+  <si>
+    <t>Converting PDF to Word is not working - Community</t>
+  </si>
+  <si>
+    <t>Batch Convert PDF to Word - Community</t>
+  </si>
+  <si>
+    <t>How can I convert a Pdf File into Word without the text boxes in word ...</t>
+  </si>
+  <si>
+    <t>Converting PDF to Excel or Word displays image instead of text</t>
+  </si>
+  <si>
+    <t>right click convert to PDF in windows 10 - Community</t>
+  </si>
+  <si>
+    <t>Spotify</t>
+  </si>
+  <si>
+    <t>强化学习算法中，PPO算法是不是就是加了重要性采样、GAE和梯度 …</t>
+  </si>
+  <si>
+    <t>PPO强化学习需要探索吗？ - 知乎</t>
+  </si>
+  <si>
+    <t>win10如何关闭雷云开机自动启动 - 百度经验</t>
+  </si>
+  <si>
+    <t>强化学习使用PPO进行训练时，总的reward只有最开始升高，后来就 …</t>
+  </si>
+  <si>
+    <t>PPO和SAC算法哪个更好？ - 知乎</t>
+  </si>
+  <si>
+    <t>如何解决PPO强化学习收敛局部最优的问题？ - 知乎</t>
+  </si>
+  <si>
+    <t>美国健康管理产业与保险业的合作方式是？ PPO是一个什么样的组织？</t>
+  </si>
+  <si>
+    <t>在强化学习中，为什么TRPO和PPO算法属于On-Policy的算法？</t>
+  </si>
+  <si>
+    <t>【深度强化学习】什么场景使用PPO，什么场景下使用DQN？</t>
+  </si>
+  <si>
+    <t>PPO已经有了reward model 为何还要有critic model？ - 知乎</t>
+  </si>
+  <si>
+    <t>Sky Go Wont Start up on Windows 11 PC</t>
+  </si>
+  <si>
+    <t>SKY GO &amp; WINDOWS 10/11 LAPTOP ISSUES</t>
+  </si>
+  <si>
+    <t>Sky go desktop app not working on windows | Sky Community</t>
+  </si>
+  <si>
+    <t>Sky go app not working on windows 11 | Sky Community</t>
+  </si>
+  <si>
+    <t>Account &amp; Billing Board | Sky Community</t>
+  </si>
+  <si>
+    <t>Sky Q Box not connecting to wifi | Sky Community</t>
+  </si>
+  <si>
+    <t>IP Adress | Sky Community</t>
+  </si>
+  <si>
+    <t>Sky Ads most annoying | Sky Community</t>
+  </si>
+  <si>
+    <t>Answered: I would like to speak to a real person at sky what.</t>
+  </si>
+  <si>
+    <t>Answered: Screen goes black momentarily then comes back on …</t>
+  </si>
+  <si>
+    <t>dge结尾的单词及意思 - 百度知道</t>
+  </si>
+  <si>
+    <t>DGE/DSGE /CGE有什么区别？主流经济学均衡分析还有哪些方法吗？</t>
+  </si>
+  <si>
+    <t>如何大致判断一个英语单词的读音？ - 知乎</t>
+  </si>
+  <si>
+    <t>英语音标中d3那个音标怎么读 - 百度知道</t>
+  </si>
+  <si>
+    <t>DSGE、OLG 和 CGE 三者之间有哪些联系与区别？ - 知乎</t>
+  </si>
+  <si>
+    <t>请问，末尾发 /dʒ/ 或者 /ʒ/ 的单词有哪些？ - 知乎</t>
+  </si>
+  <si>
+    <t>手机版edge浏览器下载路径? - 百度知道</t>
+  </si>
+  <si>
+    <t>【自然拼读phonics】lesson36 字母组合音节ge,dge发音规则</t>
+  </si>
+  <si>
+    <t>如何评价平井一夫？ - 知乎</t>
+  </si>
+  <si>
+    <t>origin做图后怎么返回到数据表 - 百度知道</t>
+  </si>
+  <si>
+    <t>EducationWorld - India's most credible school rankings Since …</t>
+  </si>
+  <si>
     <t>[found sos] cant login whatsapp browser - Lowyat.NET</t>
   </si>
   <si>
     <t>Whatsapps hacked - Lowyat.NET</t>
   </si>
   <si>
-    <t>Microsoft Community</t>
-  </si>
-  <si>
     <t>Whatsapp Desktop dah jadi fb app - Lowyat.NET</t>
   </si>
   <si>
@@ -178,460 +541,157 @@
     <t>those use ipon watsapp web browser - Lowyat.NET</t>
   </si>
   <si>
-    <t>Back up all whatsapp chat history with media to PC</t>
-  </si>
-  <si>
-    <t>Change WhatsApp number without notifying - Lowyat.NET</t>
-  </si>
-  <si>
     <t>FB, IG &amp; Whatsapp Subscriptions Are Here! - Lowyat.NET</t>
   </si>
   <si>
-    <t>What isLeadership? Definition, Meaning &amp; Importance</t>
-  </si>
-  <si>
-    <t>The 12 Characteristics of a Good Leader | CCL</t>
-  </si>
-  <si>
-    <t>Leadership-Wikipedia</t>
-  </si>
-  <si>
-    <t>Leadership: Meaning, Characteristics, Theories and Styles</t>
-  </si>
-  <si>
-    <t>What isleadership: A definition and way forward | McKinsey</t>
-  </si>
-  <si>
-    <t>What IsLeadership? A Definition Based on Research | CCL</t>
-  </si>
-  <si>
-    <t>What IsLeadership? Definition, Types, and Skills - Naukri.com</t>
-  </si>
-  <si>
-    <t>What IsLeadership? -Mind Tools</t>
-  </si>
-  <si>
-    <t>Leadership-Psychology Today</t>
-  </si>
-  <si>
-    <t>What IsLeadership? Meaning, Definitions, Theories, Styles ...</t>
-  </si>
-  <si>
-    <t>Avis sur Amazon - Forum - 60 millions de consommateurs</t>
-  </si>
-  <si>
-    <t>Forum - 60 millions de consommateurs</t>
-  </si>
-  <si>
-    <t>Amazon.de: ‚3 für 2‘ FSK-18-Filme aus über 200 Titeln</t>
-  </si>
-  <si>
-    <t>Der allgemeine Amazon Nintendo Switch Schnäppchen-Thread</t>
-  </si>
-  <si>
-    <t>Refus de remboursement de la part d'Amazon - Forum - 60 millions de ...</t>
-  </si>
-  <si>
-    <t>SAV electro dépot - Forum - 60 millions de consommateurs</t>
-  </si>
-  <si>
-    <t>Amazon Prime : l’abonnement payant après la livraison gratuite</t>
-  </si>
-  <si>
-    <t>Amazon - Forum - 60 millions de consommateurs</t>
-  </si>
-  <si>
-    <t>Amazon Haul : notre test révèle de sérieux problèmes de conformité</t>
-  </si>
-  <si>
-    <t>Amazon clôture mon compte - 60 Millions de Consommateurs</t>
-  </si>
-  <si>
-    <t>Practise Englishreadingskills | LearnEnglish</t>
-  </si>
-  <si>
-    <t>Teach Your Child To Read Early, Step by Step |Reading.com</t>
-  </si>
-  <si>
-    <t>Reading-Wikipedia</t>
-  </si>
-  <si>
-    <t>English Reading| Learn English</t>
-  </si>
-  <si>
-    <t>BBC Learning English - TheReadingRoom</t>
-  </si>
-  <si>
-    <t>Reading- Test-English</t>
-  </si>
-  <si>
-    <t>EnglishReading:English Texts for Beginners- Lingua.com</t>
-  </si>
-  <si>
-    <t>Free Online IELTSReadingPractice Test &amp; Solution Collection</t>
-  </si>
-  <si>
-    <t>Welcome to Open Library | Open Library</t>
-  </si>
-  <si>
-    <t>Reading A-Z: The onlinereadingprogram with downloadable books to ...</t>
-  </si>
-  <si>
-    <t>Education-Wikipedia</t>
-  </si>
-  <si>
-    <t>Home | Ministry of Education</t>
-  </si>
-  <si>
-    <t>EDUCATIONALDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Education.com | #1EducationalSite for Pre-K to 8th Grade</t>
-  </si>
-  <si>
-    <t>EDUCATIONAL| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Educational Games- Play Online for Free! - Poki</t>
-  </si>
-  <si>
-    <t>EducationWorld - India's most credible school rankings Since 1999</t>
-  </si>
-  <si>
-    <t>Definition, Development, History, Types, &amp; Facts - Britannica</t>
-  </si>
-  <si>
-    <t>EducationalQualification: Meaning &amp; How to Write It</t>
-  </si>
-  <si>
-    <t>Education vs.Educational— What’s the Difference?</t>
-  </si>
-  <si>
-    <t>Sudoku diabolique - Résolvez des puzzles sudoku diaboliques</t>
-  </si>
-  <si>
-    <t>Extrem Sudoku - Löse extrem schwierige Rätsel kostenlos</t>
-  </si>
-  <si>
-    <t>Play Free Sudoku online - solve web sudoku puzzles</t>
-  </si>
-  <si>
-    <t>Sudoku höllisch - Löse höllische Sudoku-Rätsel gratis online</t>
-  </si>
-  <si>
-    <t>Sudoku für experten - Tagesspiegel auf Sudoku.com</t>
-  </si>
-  <si>
-    <t>Les puzzles de sudoku les plus difficiles - jouez gratuitement au ...</t>
-  </si>
-  <si>
-    <t>Jetzt kostenlos Sudoku spielen!</t>
-  </si>
-  <si>
-    <t>Jouez au Sudoku gratuitement</t>
-  </si>
-  <si>
-    <t>Sudoku experto</t>
-  </si>
-  <si>
-    <t>¡Juega al sudoku gratis ya!</t>
-  </si>
-  <si>
-    <t>Macro500 MICRONTarpaulin Sheet Waterproof Heavy Duty 6</t>
-  </si>
-  <si>
-    <t>PlasticDiggiTirpal500&amp; 300MicronPond Liner</t>
-  </si>
-  <si>
-    <t>मैक्रो500 MICRONTarpaulin Sheet Waterproof ... - Flipkart</t>
-  </si>
-  <si>
-    <t>Mipatex500 MicronHDPE Plastic Geomembrane Fish Pond Liner</t>
-  </si>
-  <si>
-    <t>PlasticSetu · All plastic raw materials. One platform.</t>
-  </si>
-  <si>
-    <t>Plastic Carry Bag Latest Price, Manufacturers &amp; Suppliers</t>
-  </si>
-  <si>
-    <t>India Plastic Tenders, Bids &amp; RFPs 2026 - TendersOnTime</t>
-  </si>
-  <si>
-    <t>LdpeSheet- LDPE PlasticSheetLatest Price, Manufacturers</t>
-  </si>
-  <si>
-    <t>Plastic Recyclers in India | Waste Management Company | Lucro</t>
-  </si>
-  <si>
-    <t>Buy Polymers Online at the Best Price | PolyMart Pvt Ltd</t>
-  </si>
-  <si>
-    <t>Skype Account - Microsoft Community</t>
-  </si>
-  <si>
-    <t>activation du partage de son - Communauté Microsoft</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>YouTube- Apps on Google Play</t>
-  </si>
-  <si>
-    <t>YouTube Music</t>
-  </si>
-  <si>
-    <t>Movies &amp; TV -YouTube</t>
-  </si>
-  <si>
-    <t>cad的xc命令能沿着弧形边裁剪么_百度知道</t>
-  </si>
-  <si>
-    <t>西铁城女式XC系列手表如何调时间和日期？ _百度知道</t>
-  </si>
-  <si>
-    <t>不考虑经济，沃尔沃S60和XC60如何选择? - 知乎</t>
-  </si>
-  <si>
-    <t>XC 车有必要上 140mm 行程的前叉吗？ - 知乎</t>
-  </si>
-  <si>
-    <t>origin中lorentz拟合y0,xc,w,A,H各是什么意思?_百度知道</t>
-  </si>
-  <si>
-    <t>CAD中XC快捷键怎么用的 - 百度知道</t>
-  </si>
-  <si>
-    <t>已知R=3Ω,XL=15Ω,XC=11Ω,将它们串联时,总阻抗Z等于</t>
-  </si>
-  <si>
-    <t>内存卡中的“HC”和“XC”有什么区别？_百度知道</t>
-  </si>
-  <si>
-    <t>SD卡上标注的HC或XC是什么意思？_百度知道</t>
-  </si>
-  <si>
-    <t>3000-4000价位XC山地自行车推荐丨避入坑（⭐）</t>
-  </si>
-  <si>
-    <t>gitlab flow 大家是怎么优秀使用的，相关实践资料也可以？ - 知乎</t>
-  </si>
-  <si>
-    <t>说唱歌曲怎样编排flow？ - 知乎</t>
-  </si>
-  <si>
-    <t>FLOW-3D是基于什么设计的。它的计算方程是什么？ - 知乎</t>
-  </si>
-  <si>
-    <t>SW的Flow Simulation在插入边界条件时，提示“无法找到与此项目相关 …</t>
-  </si>
-  <si>
-    <t>计算机网络中，Flow和Stream有什么区别？ - 知乎</t>
-  </si>
-  <si>
-    <t>知乎 - 知乎</t>
-  </si>
-  <si>
-    <t>说唱音乐里面的「flow」是什么？ - 知乎</t>
-  </si>
-  <si>
-    <t>有没有大佬知道traffic volume 与traffic flow 的区别？ - 知乎</t>
-  </si>
-  <si>
-    <t>苹果开始抛弃 Cover Flow 视图是明智的决定吗？ - 知乎</t>
-  </si>
-  <si>
-    <t>如何理解associative flow 和 non-associative flow的区别？</t>
-  </si>
-  <si>
-    <t>chat-gpt-app · GitHub Topics · GitHub</t>
-  </si>
-  <si>
-    <t>GitHub - kx-Huang/ChatGPT-on-WeChat: ️ Deploy GPT-4o …</t>
-  </si>
-  <si>
-    <t>不是说chat gpt是免费的吗，怎么只能免费问一次? - 知乎</t>
-  </si>
-  <si>
-    <t>Chat GPT Tiếng Việt: Cài đặt và mẹo đặt câu lệnh mới nhất</t>
-  </si>
-  <si>
-    <t>chat GPT 为什么在购物平台上被封杀了? - 知乎</t>
-  </si>
-  <si>
-    <t>Supported AI models in GitHub Copilot</t>
-  </si>
-  <si>
-    <t>Changing the AI model for GitHub Copilot Chat</t>
-  </si>
-  <si>
-    <t>So sánh AI Hay và Chat GPT cái nào tốt hơn? - CellphoneS</t>
-  </si>
-  <si>
-    <t>Chat GPT World Builder Prompt · GitHub</t>
-  </si>
-  <si>
-    <t>ChatGPT Overused Words &amp; Phrases · GitHub</t>
-  </si>
-  <si>
-    <t>求解释，microSD卡的参数什么意思？如图，HC XC差别，还有下面 …</t>
-  </si>
-  <si>
-    <t>捷安特Xtc800有什么好的，感觉一般般啊？ - 知乎</t>
-  </si>
-  <si>
-    <t>CAD中用xc的剪切的图形复原 - 百度知道</t>
+    <t>Saifuddin's Whatsapp kena hack - Lowyat.NET</t>
   </si>
   <si>
     <t>Riana @ dutamas by IJM.....</t>
   </si>
   <si>
-    <t>File Explorer in Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Explorador de archivos en Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Show or Hide Preview Pane in File Explorer in Windows 11</t>
-  </si>
-  <si>
-    <t>how do i bring back the old windows 7 file explorer back to …</t>
-  </si>
-  <si>
-    <t>Explorateur de fichiers dans Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Explorer in Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>File Explorer di Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Fix File Explorer if it won't open or start | Microsoft Support</t>
-  </si>
-  <si>
-    <t>File Explorer trong Windows | Microsoft Support</t>
-  </si>
-  <si>
-    <t>OneDrive help &amp; learning | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Google Images</t>
-  </si>
-  <si>
-    <t>Google Translate</t>
-  </si>
-  <si>
-    <t>Google Maps</t>
-  </si>
-  <si>
-    <t>Google Videos</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Google for Education - Online Resources for Teachers &amp; Students</t>
-  </si>
-  <si>
-    <t>Google Books: Find, Preview, and Read Books Online.</t>
-  </si>
-  <si>
-    <t>Google - Moving on from Picasa</t>
-  </si>
-  <si>
-    <t>Google Assistant, your own personal Google</t>
-  </si>
-  <si>
-    <t>SQLite数据库查看器 DB Browser for SQLite 3.12.0 中文绿色版 - 吾爱 …</t>
-  </si>
-  <si>
-    <t>DB Browser for SQLite 3.12.1 中文绿色版 11/9更新 - 吾爱破解</t>
-  </si>
-  <si>
-    <t>更新版本_SQLITE管理软件DB Browser for SQLite 版本 3.13.1 - 吾爱 …</t>
-  </si>
-  <si>
-    <t>独家食用指南系列|Android端SQLCipher的攻与防新编 - 吾爱破解</t>
-  </si>
-  <si>
-    <t>Sqlite各版本x86&amp;x64安装包 - 吾爱破解 - 52pojie.cn</t>
-  </si>
-  <si>
-    <t>微信数据库解密的一点经验 - 吾爱破解 - 52pojie.cn</t>
-  </si>
-  <si>
-    <t>安卓中道具修改,仅以此片献给菜鸟朋友们 (DB Browser for SQLite简易 …</t>
-  </si>
-  <si>
-    <t>SQLite数据库可视化管理编辑器 SQLiteStudio v3.4.4-amd64 - 吾爱破 …</t>
-  </si>
-  <si>
-    <t>家庭就诊记录管理系统 - 吾爱破解 - 52pojie.cn</t>
-  </si>
-  <si>
-    <t>Sqlite数据库管理器 SQLiteStudio v3.4版 - 吾爱破解 - 52pojie.cn</t>
-  </si>
-  <si>
-    <t>Biziverse ERP &amp; CRM Software serving 40,000+ Indian MSMEs</t>
-  </si>
-  <si>
-    <t>Biziverse Tutorials</t>
-  </si>
-  <si>
-    <t>LEIP - Biziverse</t>
-  </si>
-  <si>
-    <t>Policies - Google Docs</t>
-  </si>
-  <si>
-    <t>Biziverse | Training | Videos &amp; Live Sessions</t>
-  </si>
-  <si>
-    <t>Biziverse</t>
-  </si>
-  <si>
-    <t>Biziverse ERP &amp; CRM Software</t>
-  </si>
-  <si>
-    <t>Open File Explorer in Windows 11</t>
-  </si>
-  <si>
-    <t>Windows 中的文件资源管理器 | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Windows help and learning | Microsoft Support</t>
-  </si>
-  <si>
-    <t>Download &amp; use Google Translate</t>
-  </si>
-  <si>
-    <t>Translate website to any specific language, on page load</t>
-  </si>
-  <si>
-    <t>How to remove punctuation marks from a string in Python 3.x using ...</t>
-  </si>
-  <si>
-    <t>301 Moved</t>
-  </si>
-  <si>
-    <t>html - transform:translate (10%)とするとずれる。 - スタック・オー …</t>
-  </si>
-  <si>
-    <t>KASKUS</t>
-  </si>
-  <si>
-    <t>Angular ngx-translate usage in typescript - Stack Overflow</t>
-  </si>
-  <si>
-    <t>CSS tranform:translateY from JavaScript - Stack Overflow</t>
-  </si>
-  <si>
-    <t>html - Transform: translate (-50%, -50%) - Stack Overflow</t>
-  </si>
-  <si>
-    <t>How to translate one language to another using java code</t>
+    <t>Why someone instantly see WhatsApp message? - Lowyat.NET</t>
+  </si>
+  <si>
+    <t>PSA: Beware of .vbs file scam - Lowyat.NET</t>
+  </si>
+  <si>
+    <t>West Bengal Govt Jobs2026 Notifications (1428Vacancies) on …</t>
+  </si>
+  <si>
+    <t>WBGovt JobsWB2026 | পশ্চিমবঙ্গ সরকারি চাকরি —West Bengal</t>
+  </si>
+  <si>
+    <t>Latest West BengalGovernment Job Notifications | FreeJobAlert.Com</t>
+  </si>
+  <si>
+    <t>DistrictRecruitmentJobsWB2026 | জেলা নিয়োগ —West Bengal</t>
+  </si>
+  <si>
+    <t>Public Service Commission,WB</t>
+  </si>
+  <si>
+    <t>Recruitments | WBPRB -West Bengal</t>
+  </si>
+  <si>
+    <t>West BengalGovt Jobs 2026 – 1,085Vacancies(8 Oct) | Sarkari Naukri</t>
+  </si>
+  <si>
+    <t>West Bengal- Home | WBPRB</t>
+  </si>
+  <si>
+    <t>West BengalPolice</t>
+  </si>
+  <si>
+    <t>Time in India - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Current Local Time in Coimbatore, Tamil Nadu, India</t>
+  </si>
+  <si>
+    <t>Current Local Time in New Delhi, Delhi, India - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Current Local Time in Kochi, Kerala, India - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Current Local Time in Nashik, Maharashtra, India</t>
+  </si>
+  <si>
+    <t>Current UTC — Coordinated Universal Time</t>
+  </si>
+  <si>
+    <t>Current Local Time in Kolkata, West Bengal, India</t>
+  </si>
+  <si>
+    <t>Current Local Time in Agra, Uttar Pradesh, India</t>
+  </si>
+  <si>
+    <t>Current Local Time in Dubai, Dubai, United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Time in Punjab, India - timeanddate.com</t>
+  </si>
+  <si>
+    <t>Reading A-Z: The onlinereadingprogram with downloadable …</t>
+  </si>
+  <si>
+    <t>r/ChatGPT's FAQ Thread - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPT最实用的提示（Prompts）写法有哪些？ - 知乎</t>
+  </si>
+  <si>
+    <t>ChatGPT for Legacy iOS - GitHub</t>
+  </si>
+  <si>
+    <t>chatgpt-api · GitHub Topics · GitHub</t>
+  </si>
+  <si>
+    <t>awesome-ChatGPT-repositories - GitHub</t>
+  </si>
+  <si>
+    <t>ChatGPT-Bypass - GitHub</t>
+  </si>
+  <si>
+    <t>WhatsApp Web</t>
+  </si>
+  <si>
+    <t>DownloadWhatsApp</t>
+  </si>
+  <si>
+    <t>WhatsApp| Secure and Reliable Free Private Messaging and Calling</t>
+  </si>
+  <si>
+    <t>HOUSAB -WhatsApp</t>
+  </si>
+  <si>
+    <t>AboutWhatsApp Web|WhatsAppHelp Center</t>
+  </si>
+  <si>
+    <t>WhatsAppMessaging</t>
+  </si>
+  <si>
+    <t>WhatsApp-Wikipedia</t>
+  </si>
+  <si>
+    <t>How to downloadWhatsAppDesktop |WhatsAppHelp Center</t>
+  </si>
+  <si>
+    <t>WhatsApp Web-WhatsAppBlog</t>
+  </si>
+  <si>
+    <t>TéléchargerWhatsapp Web(gratuit) pour ordinateur -Clubic</t>
+  </si>
+  <si>
+    <t>Hazrate Haleema Sadiya ne Hamarenabiko saath me Liya/Mufti …</t>
+  </si>
+  <si>
+    <t>sahezadi.. (@miss_nobi_011) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>pyarinabiKY pyari shehzadi maa fatima ️ #duet - YouTube</t>
+  </si>
+  <si>
+    <t>official ________sahezadi(@official_____sahezadi) - Instagram</t>
+  </si>
+  <si>
+    <t>Manjari (Indian singer) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Mufti Furkan Razamanjaritaqrir baiyan नबी ए पाक के वालिद की शादी में ...</t>
+  </si>
+  <si>
+    <t>ShehzadiNabi- Facebook</t>
+  </si>
+  <si>
+    <t>Sahezadi(@sahezadi20250) | Snapchat Stories, Spotlight &amp; Lenses</t>
+  </si>
+  <si>
+    <t>Shehzadi e Rasool Jannat ki hai Malika Lyrics</t>
+  </si>
+  <si>
+    <t>ManjariFadnis Full Profile - Bio, Body Stats, Dating Life &amp; Net Worth ...</t>
   </si>
   <si>
     <t>Youth &amp; Tutoring</t>
@@ -640,601 +700,658 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>ofm@amazon.fr</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d7cad9ef980232d51bda7753992e7a6b9672bdd5e4d88f616278026340319fdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTk0OTIyNi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d9273b17e49bba685cd535a2276351ed3ba4f7dc94192f179cd978b0bb649f1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj13TWNxNElPa2NlQQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a12f4150a08914a61ea7a845e92aa35c5eb099564b59262ffc717ddc679457b1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=411fea06758d517b891c8aed73b93f29aa977df3883bba01f5c7a963f9aa94abJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38df0f07b8a5f5a34553e7793dd488e635669b978315bd3bc1cda993a6322fbdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1qWkVBMm1Nd0wxaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80f649bf67cbf5bf1684048f821ab72ddf21dbf2ed36147b8cce135cfb56c44fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKDIwMjZfZmlsbSk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21b74a000e32602fca4952943c25bc33d456152429f8e659a5e0c00de5eca26bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cuaGlnaG9uZmlsbXMuY29tL3lvdXRoLXJlbGVhc2Utc2NoZWR1bGUtZXBpc29kZXMtY2FzdC13aGVyZS10by13YXRjaC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dfd24511958acf05bf285ff2fe2485704f18c6a9a88bfb22ece4a532e5eddb0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly9teWJoYXJhdC5nb3YuaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64aabf75850bc8e5d68e2454f0a65006ee6d23c13d1ba763f581bb0c4fb267dfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly95b3V0aGh1Yi5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab6f83136a7196207db72a12ab7794d6ad71d0e03f34fc6a0d57a1518dc6a006JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2144c59a-0f7a-6387-1618-d2760e0e62c4&amp;u=a1aHR0cHM6Ly93d3cubW9zcGkuZ292LmluL3NpdGVzL2RlZmF1bHQvZmlsZXMvcHVibGljYXRpb25fcmVwb3J0cy9Zb3V0aF9pbl9JbmRpYV8yMDIyL092ZXJ2aWV3LnBkZg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38b49a690c2945d5549f410c17f8d60474ffae3b8d59eb27bddabe8cd14e83bbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9ob3ctdG8tZ2V0LWhlbHAtaW4td2luZG93cy03MTFiNjQ5Mi0wNDM1LTAwMzgtODcwNi03YzZiMGZlYjIwMGE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9dbcab0a27c84cf3598afff02a28807aef6a0af29228f5c51d58ac72a049108aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9b7d36b3d7f47458888e92ba45909c203199faba2153c90a4dd7ab5e5fd956eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebcc412c3a4051302e6d3724aa0f98d3dd65aef63f5bb691fc9931240d862ca7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tL3QvZW5hYmxlLW9yLWRpc2FibGUtdGlwcy1hbmQtc3VnZ2VzdGlvbnMtbm90aWZpY2F0aW9ucy1pbi13aW5kb3dzLTExLjUyMDYv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0364afc0d70161791808686dfddf57295cfeb3cefb6f0fead16021e97030f143JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vamEtanAvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bf2ef04b71163c3a7533d918cd4c5ac340c8100681a347be34c5fb217e126bdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b02cb4900be96b41373efce442ccbf52b04f07f75c5962b30192347eab1c7dbbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vcHQtYnIvd2luZG93cy9jb21vLW9idGVyLWFqdWRhLW5vLXdpbmRvd3MtNzExYjY0OTItMDQzNS0wMDM4LTg3MDYtN2M2YjBmZWIyMDBh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6553d19fd9598a47267239d70d8755d84277b206f9d03b3991e39f543fae54fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19d1361b90714ef716da1ed77d08c6afe7430b12dcc63bdbfab83e60e782dc95JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vemgtdHcvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cbecab0ea57fe8e8914d0e650481f31c711aacb224ee7b17af80e0972f9339cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37756246-379c-62a6-248d-75aa36f96302&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvc3VwcG9ydC9nZXQtaGVscC9ydW5uaW5nLXRyb3VibGVzaG9vdGVycy1pbi1nZXQtaGVscA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09b814d61aa56a372f496f9d2b8ab2cbda51e0b610270e15672d8174a8c97694JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfKGZpbG1fc2VyaWVzKQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23c7d40900f7d919ce73c1f17eea7ed2417c18dc69d6bb6301679fefee13cfcaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L3doZXJlLXRvLXdhdGNoLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce76623d7c6024ca517b3337f1c018062c609ef0a11b875e274f21f66798b514JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODAyNDQzMTE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=565203aa675bc7c39ff10980751d1159aeb437a31ca411852ac054b00510e3c4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9hZnRlci0yMDE5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a5c189f38ce604c080bf3dffdf57f7dfaf9f95a6b5026f83f4b76b1bd6478fdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly92aW1lby5jb20vMzM2ODUxNTI2P21zb2NraWQ9Mjc1NjlmOGE5ZGU3NjcwYzEyYTk4ODY2OWNjOTY2MDg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e91e706539d4bf148111c513642f2f8704c4c45b1404dd8406402f440c330881JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly9tb3ZpZXdlYi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df6e89df9288748784266a73767a87cad6149f198cb7c9407dd17cc21ad91bd0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ0MTI2NDc2L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=773f0f2b79e33d7cae9731ac935c93abcabb144b704d3d301b8be74fb774de5cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfJTI4MjAxOV9maWxtJTI5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c73375f9d10ce8ed28fdd1274f1bfdafc316b1718b5f35c1037f796cdbe085aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vbGlzdC9sczUyMTQwNjQwOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2348a282083d6d8876307a606a14a1e26be236b4a2af8bcc9c01ccdcf7f60010JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27569f8a-9de7-670c-12a9-88669cc96608&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L21haW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b746883b76961c86b3a26d538bc082b38d355c4d5d79aff86432428a7c3c54fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac435cab0e910379233a758f6a9f087c0e0282f4c91e913996a2a1cdc1012640JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeS9uZWVkLWtub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6eef068b356650916649471d3749b951a799e2bc80d849bbb627f5e75d94edbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78da7e8914c727b3976862a3fa59e8055ae332e19c032859598d6daffdf611f2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2c8406b27c647e26adc49294f59a7de52dd52c0c4067ee4cfe366495fb7b066JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3lfaW5fSW5kaWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=295c30caa20a2b6c16e931340e624f284862e0c167baf8ff8c2e12b72fb1e5d0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly9vdXJ3b3JsZGluZGF0YS5vcmcvbGl0ZXJhY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca772cba4122c07c26ce00073d4feb7956fc4d45571528516df5acc7a8483465JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2xpdGVyYWN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=439460b5237c1401388cb617cf376e9920da1ed074edb2dec48df4e0905ed9e8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly9saXRlcmFjeXRydXN0Lm9yZy51ay9pbmZvcm1hdGlvbi93aGF0LWlzLWxpdGVyYWN5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd8ace849c3e54d426bc53e67f6cd7a6045fd20d6d897db814bdf8736f742f1dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly9pbmRpYWNlbnN1cy5pbi9saXRlcmFjeS1yYXRlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=761e79e2d6b00dff8d8f188250c23eeea8d031988076b602f8b6a58bdf1fc40bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c39e12f-1670-6919-0776-f6c3179e68f3&amp;u=a1aHR0cHM6Ly93b3JsZGxpdGVyYWN5Zm91bmRhdGlvbi5vcmcvdGhlLWltcG9ydGFuY2Utb2YtbGl0ZXJhY3kv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd69b2aeedf5dd5e3d4d622b87707829df78b93a58ce9ddc8603331ebc7708acJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c074ed9b3e3a3d6fff2b3d2328095642b627b8afdbdaa8d54a86e3619e8c5dceJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1MTk4OTg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acb4b8a0e23d9b210ec95ded34222dfc46f32a3578b3adb9e5a119797a09164bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9mb3J1bS9hbGwvbWF0c2hpdGEtZHZkLXJhbS11ajg5MGFzLWZpdHRlZC10by10b3NoaWJhL2UxZDc3MDgzLTQ1OTgtNDk5YS04Zjk1LTE5OGFhZGY1ZTA2Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0492b568010f79f0bc977d0a81cbe2d5e0760f5a645b4c93345937f2b7ff6be8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjUxOTA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a00188cdde95f4837f7f50ffb57cc90edf77aefdce9e99f77acccd3e85c7a617JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1Mzg3Mzg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9f4eb928ef55d72df49eb4713d71a4c6a9caa88db6b1daf0682263c35fd6c3fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b97dc4b4d017492342d83cb44e4bb83f9c1d93f35ddd94255826e566f62aeaa1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMzODI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0428fd9c45b8e0e0799a3e1978b7eba900bcec6fda4f602ed081d81ccec6d3a0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMxODc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24568c125c2b7f7700450098b7e0c7d227a094a07953bc0d8b6097757deb56f6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d91c0c5-db89-6aae-19f4-d729da1c6b1c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjYwODA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e81579323d7e3cd4a76bf84280633257e4320be70e96c011371b33f422efebbdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly9lbWVyaXR1cy5vcmcvaW4vbGVhcm4vd2hhdC1pcy1sZWFkZXJzaGlwLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2481e8420349c2cf41df153aa1ea8744445c0c9453621ca380301d718db3d23eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL2NoYXJhY3RlcmlzdGljcy1nb29kLWxlYWRlci8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72a2edeca92b988b185b08bd04f934f49ee28b16e6352f2d06c81082b1e02c61JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MZWFkZXJzaGlw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=696e6193fad96ba6e6154671fa520293b15a8284ca4d103ec3f20f483908f963JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cubWFuYWdlbWVudHN0dWR5Z3VpZGUuY29tL2xlYWRlcnNoaXBfYmFzaWNzLmh0bQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e555cea7d30b29db18aa7b2b41a2a8c687c24dab26aae3fb7443fecc02ccce1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cubWNraW5zZXkuY29tL2ZlYXR1cmVkLWluc2lnaHRzL21ja2luc2V5LWV4cGxhaW5lcnMvd2hhdC1pcy1sZWFkZXJzaGlw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9dee2711e7643ae65aab11675b4e3281a8f2ed392b71b98297a9ebb2cce9129JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL3doYXQtaXMtbGVhZGVyc2hpcC1hLWRlZmluaXRpb24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f1320d9c1e0da9c9cfc969816ce94df1ae0c88ef761394ad11cf5836d847f00JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cubmF1a3JpLmNvbS9ibG9nL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd1ecf7c166744fff859b20bd18e36564c98b12bedda48fd1fad165246fba21aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cubWluZHRvb2xzLmNvbS9hMmZqc2oxL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20967b8f351a5c334e3f3db21b728667054a1960883cf6a70170cd3dd598dd0fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvbGVhZGVyc2hpcD9tc29ja2lkPTBiNzRkYTczOWJkYjYwNjgxY2Y1Y2Q5ZjlhNzE2MTM5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a534339324434d79ad76aacd1129c606cb11718382bde17fa7d7ef29e5ed8821JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b74da73-9bdb-6068-1cf5-cd9f9a716139&amp;u=a1aHR0cHM6Ly93d3cuZ2Vla3RvbmlnaHQuY29tL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9aa01447236df9429e3b8226b8aaf42c082d3ab2dbb167184345677bac7b7b0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvMjkwODktYXZpcy1zdXItYW1hem9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b6282c427382a718e74ceb5d750120022694a8db0498cb6cde3e7fe53b7fd63JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74183c18256b824a6bd8b4f1b9ee953f22b3cfbdd5e46a2904494397ac1df31fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuZHZkLWZvcnVtLmF0L2FtYXpvbi1kZS0zLWZ1ZXItMi1mc2stMTgtZmlsbWUtYXVzLXVlYmVyLTIwMC10aXRlbG4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=143d66ff468152ab85fdc73bf2697d3c0f3bf8d7771a20d64eaec8046938aaf8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuZHZkLWZvcnVtLmF0L2NvbW11bml0eS9hbmdlYm90ZS1zY2huYWVwcGNoZW4vZGVyLWFsbGdlbWVpbmUtYW1hem9uLW5pbnRlbmRvLXN3aXRjaC1zY2huYWVwcGNoZW4tdGhyZWFk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6be6fb78d5fe9a58a0e31227d473fdf12f1fcd44a4850195141ed7ee6af71c88JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvMTkwNjA3LXJlZnVzLWRlLXJlbWJvdXJzZW1lbnQtZGUtbGEtcGFydC1kLWFtYXpvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=672139c0de082c2a38d0d5c334a634b80613d4003a649c5b6ed0e7f92c2523eeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvNjE1Ny1zYXYtZWxlY3Ryby1kZXBvdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f5b442c6b58a300b4f0cdcba3417eff9ae923b3dbf9ae090ab71e9adb29cd33JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2NvbW1lcmNlL2FydGljbGUvYW1hem9uLXByaW1lLWwtYWJvbm5lbWVudC1wYXlhbnQtYXByZXMtbGEtbGl2cmFpc29uLWdyYXR1aXRlLTIwMTkwMjI3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbc1b918a4376d243ae0d1426fd59c4029bb6475e13e54b88bbad1ceb2630c11JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvMjU5NTM1LWFtYXpvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3b0383cd7e2540b813e132b8ec3f149f319f3e8c7dcd71dcb5393ed803e78a5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2NvbW1lcmNlL2FydGljbGUvYW1hem9uLWhhdWwtbGEtZm9pcmUtYXV4LXByb2R1aXRzLW5vbi1jb25mb3JtZXMtMjAyNjA1MDYv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5683f4650fb6a310c347c6ed5446d5ee75c1e03cbc870409969a7c809bfa2393JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvMjA4NzM3LWFtYXpvbi1jbG90dXJlLW1vbi1jb21wdGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72487174ef98d68b3bc604c4f26db6baf7fcb4aecd02d71101342104e8c84583JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly9sZWFybmVuZ2xpc2guYnJpdGlzaGNvdW5jaWwub3JnL2ZyZWUtcmVzb3VyY2VzL3JlYWRpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=665046ab77be3519a851a8de7f611b9d387ea3377bda24d886f1e34a7058f745JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0be3a87825cd44e6456468f6d718100cda8c7d35007e05328b3c818d1962b45cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmVhZGluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcb6343d6c3bd4fbf801d454d3d5e21217c6ad27ddefeb96973377cc94e44456JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGlzaGNsdWIuY29tL3JlYWRpbmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d7a36e8a7f5e948fc52930b901c4f677b3f8f73d0bf4e0f18b97e936f5e72feJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL2xlYXJuaW5nZW5nbGlzaC9mZWF0dXJlcy90aGVfcmVhZGluZ19yb29t&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84a3ef18a991e0d40b6d4c19faf10769763ae2cbd745a6ab58cfaf6e3cdf5858JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly90ZXN0LWVuZ2xpc2guY29tL3JlYWRpbmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=617d5a68e42438a03e866386602381e1c9456dfb9235c31ffd883cd54a79be62JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly9saW5ndWEuY29tL2VuZ2xpc2gvcmVhZGluZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d54ab64c6bf1a1633835b0216832f2b47489cb99123b79e260a28202a80d9b6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly9lbmdub3ZhdGUuY29tL2llbHRzLXJlYWRpbmctdGVzdHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42b16d202c69332be591a09b094b7c1471bfeb0f3e4aaf76ad30cb16db52f428JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly9vcGVubGlicmFyeS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72d4eb886dcc88b8916a3944de6d833e050bedd6179bf2ce0133a7f7465dea50JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34db475e-c04e-66e6-0f91-50b2c1a06760&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ2Etei5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37b58f0798de2295552f39d63af420913a8447890a857fda45f8751aa9445be6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FZHVjYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdf5e98f2adf99b46ba1b050c5ff37fea01c47e7e09c4746f2f9ca13a696fda0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmdvdi5pbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9ea5ae04ad9523e1ee6802faafe8b10be3a9052922b2ed32935d8aaef6ceb2cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539afd1ebc8585fd4290ee72760e132787384a044b9fa311c73298f592e369f4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS8_bXNvY2tpZD0xNGZmMmU5MjNlZDU2NjVkMmZjZTM5N2UzZjYxNjc5Mw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ee92dc9c064c39e460011e773ba648e8733ee30f6dd8c4fe9631aae7b2f81d5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VkdWNhdGlvbmFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=498f0d353efce9602ae2f42bfaac491ac98abcb94585971dac4367a875c7dc06JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS9lbi9lZHVjYXRpb25hbD9tc29ja2lkPTE0ZmYyZTkyM2VkNTY2NWQyZmNlMzk3ZTNmNjE2Nzkz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4099e923dcf6f6886aa5763d8ee825af6c4648b7deb051465509c491310c1d0dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb253b3JsZC5pbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7cfc4f397cb8d132670162f9a73c8d7268580b3fa736ad7e48dbbbd4e7a2737JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZWR1Y2F0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1a982a9a002e5555f6263dd16f845cfc71f21f5693a420975e8616d4111b33aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cuM3VuaXZlcnNpdHkuaW8vbGVhcm4vZWR1Y2F0aW9uYWwtcXVhbGlmaWNhdGlvbi1ndWlkZS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=612122fe0bf31f82c321e9cdf1b1f1b6502e759853cad40e5486f6242591794dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14ff2e92-3ed5-665d-2fce-397e3f616793&amp;u=a1aHR0cHM6Ly93d3cuYXNrZGlmZmVyZW5jZS5jb20vZWR1Y2F0aW9uLXZzLWVkdWNhdGlvbmFsLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26879162b28959eb0995c1387f4b96348fb1d711f4c42011f0e75bfe68006ce1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2ZyL2V2aWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16a1361a2e485941d0ed87a949204007f66122ab960629d02a1231f7bb1037baJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2RlL2V4dHJlbWUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=546e0a8d782dfe634d0a53993a0b3eeb9f2c9f1b82171f831210099d8d343008JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f0dee3fd0693d24113d4764663dadc0f711aa29d13710ad5a4f885fbf893dbaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2RlL2V2aWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f91008fff2b391cebe74afc590c9b7b938302ccd511b17eb10fea679c1e9e410JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2RlL2V4cGVydGUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8d950650c62bf0e60bf8a13f3af1ff4a76bf06b15d6412925f94604a72c36efJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2ZyL2V4cGVydC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=591768192acdcec94b2cd3e3e1a22f8a70be9beaba63e07d536c9f1fd4a2c3d7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2Rl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6121e7e3e2bddfc0ad89624046b96f66053dad388448ad422b067d8a38515721JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2Zy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3c4604b08e10a9b3345229093f2a99562d6fcf6662a26d857e9d6a7ad14ffaeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2VzL2V4cGVydG8v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75018049494c82e84f9fa223676995d1bf7704e0168422167966effe74390aecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=336f49e8-fda7-68e8-01f5-5e04fc6e6989&amp;u=a1aHR0cHM6Ly9zdWRva3UuY29tL2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb4455f61b0f95c4046979a34fd0d568ebd83b7ba805912d595c22e8ddbae5d6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cuZmxpcGthcnQuY29tL21hY3JvLTUwMC1taWNyb24tdGFycGF1bGluLXNoZWV0LXdhdGVycHJvb2YtaGVhdnktZHV0eS02LW1ldGVyLXgtNTAtdGVudC1wb25kLWRpZ2dpLWZpc2gtcm9vZi10b3AtZ2FyZGVuL3AvaXRtNDdlNzI0YzQzN2U0Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=118edee0e536b08b278e9cebc1237ed97d6e3a2553d97aef32b1e200ecf5a342JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cuYmhhcmF0c2VhbC5pby9tYWEtdmFpc2huby1wbGFzdG9wYWNrLXB2dC1sdGQtdTI1MjA5cmoyMDE1cHRjMDQ4MTc0L3Byb2R1Y3RzLzI3YzkyYWIyLTE1NjktNGQwYi05ZDhkLTRiOGUwNzNlYTBhMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=132b13d31c3a2b167be5d08d9da356ba0546771514c9231c0e9286efb782e6ceJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cuZmxpcGthcnQuY29tL2hpL21hY3JvLTUwMC1taWNyb24tdGFycGF1bGluLXNoZWV0LXdhdGVycHJvb2YtaGVhdnktZHV0eS02LW1ldGVyLXgtNTAtdGVudC1wb25kLWRpZ2dpLWZpc2gtcm9vZi10b3AtZ2FyZGVuL3AvaXRtNDdlNzI0YzQzN2U0Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03e7bbb4efcf23b45bc90cfca1b840d7ed4ac0653522141e83992bb10a9d5f00JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmluL01pcGF0ZXgtUGxhc3RpYy1HZW9tZW1icmFuZS1CYWNreWFyZC1XYXRlcmZhbGwvZHAvQjA4NjFSWFlMSA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d36526229a0aacff4d81459e0e30013c4ca1fb7eb5feced1fe64b2684ff816eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cucGxhc3RpY3NldHUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3b337b41ca980ac2b7aa1ff184ff31e7f6b35dec8b412263f5420fda9de0f69JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly9kaXIuaW5kaWFtYXJ0LmNvbS9pbXBjYXQvcGxhc3RpYy1jYXJyeS1iYWdzL3RoaWNrbmVzcy01MS1taWNyb24tcTE1NDg5Njk4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7def3d1e2bbc71d2e8fad94d95b7d617822d603381e5b64bdc9cfe65b1a6b78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cudGVuZGVyc29udGltZS5jb20vaW5kaWEtdGVuZGVycy9wbGFzdGljLXRlbmRlcnMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1483769ae4685700f0b1d46fa2119e10a1b5b38bc0440c8ca95c384ded90de93JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly9tLmluZGlhbWFydC5jb20vaW1wY2F0L2xkcGUtc2hlZXQuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77e40f63e81cdd2ec0909f7d191561056e7e1c3099409f5ba63c0c44d75b0cb7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly9sdWNyby5pbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b821046a21f48199a8cb79390c4fd5b46cf5303ea839ed83290a4f26fc378f18JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3451207f-b4b9-69b7-3b5a-3793b570682e&amp;u=a1aHR0cHM6Ly93d3cucG9seW1hcnQuaW4vYnV5ZXIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de8df5a165119983ef61e60694eabc18e4959ca253f3a132f1430ad28f8bafa9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a6c650f-f901-6cc3-198f-72e3f8756d41&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZGUtZGUvc2t5cGUvZm9ydW0vYWxsL3NreXBlLWFjY291bnQvYzM2OTllMzctMjU1NC00NjIwLThmMTAtZDBkMDNhMThlNDM1&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=feb6732ea9feaa9fde04175e2c008ee325a315ebc6d02081daeea96eb76c67c3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a6c650f-f901-6cc3-198f-72e3f8756d41&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZnItZnIvc2t5cGUvZm9ydW0vYWxsL2FjdGl2YXRpb24tZHUtcGFydGFnZS1kZS1zb24vNmFhYjQ5NmEtYzIwNC00OGNlLTk3NTEtMzJmOTBiZDc3ZTI0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16308f5656defce3717c1f3ed6c810731c29e36d03cfac45f1738a13924f70b5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1aaebf2e-c1eb-6ef7-1c36-a8c2c0386fcb&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vP2dsPUlO&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0eadd2920c8ff718544642e95512df49a2b6814d0da6e1e7b634a4ab5d7cf40JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1aaebf2e-c1eb-6ef7-1c36-a8c2c0386fcb&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5nb29nbGUuYW5kcm9pZC55b3V0dWJlJmhsPWVuLVVT&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=287925a1e6855aa6e47ceced13547ae8eaae0f5df3365ea8343447c9d2dafa9fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1aaebf2e-c1eb-6ef7-1c36-a8c2c0386fcb&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1aa44446d31c08484c48e25311467e2abd3de373560dc2316f3a7b2b2f3c0386JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1aaebf2e-c1eb-6ef7-1c36-a8c2c0386fcb&amp;u=a1aHR0cHM6Ly9tb3ZpZXMueW91dHViZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba19281dd12c9a8ce077eb286cc4d95a5a9a9568c6dadf86c81ee5428d0895abJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzMwNDgwMDEyNzc5OTIyMDc2NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29cc4f20c260ba38573c581b0812bdc41274b7967b3c54bb41e1e1303968eea4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzc1MjYyOTcyODUyOTgyNDE2NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8593158452ea776b33ba170b2af221e03e71591a79ad687d80e5e4ac092a84aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzQ2NDY2Njg3NA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72daa6cfd8bcb4a4b231061d8992d873bc766eff8560bc24ce681ca618cb8ffdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU1Nzg2MDc0NA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f80af3da29800e22b99e180ffe9e57ccb942dede29e9479c59edb886eadebd8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzMzODE4OTczNS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54b6f99715397796bf7ea8056dbe3d281609f64cafdfb0a1f3de18fb603648fdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzI5NzQ4NTg1Ni5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=817802b6a58507f364a0d6ce9d0ff2b6a61234c47bcdf1fc6ce2368dfaea80e7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzUwNTIxNjA3OC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2638a02b3c8777e8e876f73db6f88f66b7cd5a7e961d76997b53c526532a1f6cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzE0MzYyMjk2MDIyNzU5MzI0NTkuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56c6b7fe949e5ef5e63a6038bc039260f60db85f3e9430caec34de8b9b5c772cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzQ5MDYzNTA1NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dc5d3d46bca0031d994d2e69f4db46dd4859093d524aef0b03c1e425786def7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39507e87-70c6-6b0d-0175-696b716b6a46&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RhcmRpcy9iZC9hcnQvNjMyOTM4ODAx&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16511e2b5af220120cfc4a8e7c80928b8c2828b177020064d1dc18f290ff5f8dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMyMjU3NDU4MQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e876ea857e5b4ce45e0f985d8108530bea26c9b7f66553cdcba572de167f9502JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzI2NjY1MjgyOA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3ee6d88f39cc796474b6dcd2de9a5a77b14c0b630b86c00436558d8ca1a551dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIxODQzMTYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c3c8fab49932e36dfd653376c56815bce706b1291d105bf2123c44e7a6fa6ecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIzNzIxMDQ2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29740fe257693780c3a84915d016d3b37fc0f2d213c5d07c8807b27996538d97JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM4NzEwNDU2P3NvcnQ9Y3JlYXRlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9ee5566d94d3c632b034880a25d56d68229aed3107fc137c1ce24fb39361d2fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzY3NjQ5OTgzMTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c99f0b1c3153b0c04db2363b09f5cce093072ef85eb4f18a2c4824326cb1ee8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzE5NzI2ODIzL2Fuc3dlcnMvdXBkYXRlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6221865864b29e9bafcc32fa29155e59e7dc6621305042192328c319b5f3f493JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzYyMzg3OTcz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=919feaca97b2297b640e5c695479548f19857268080032f5da043d1a08069bd8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNjM4MTgw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11868c6cf7e2285be5d4cd014158dea40e62a39529a52d440f70bb6d627c93edJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c4e0387-3cd0-6b1b-08ea-146b3dfe6a6a&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM0MzEwOTEwMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69a8baa564b3b0d855a7ef5fa448b19799c26c4b0b3ecb6559188dd6977bbae0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0LWdwdC1hcHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95a9ed2b9add4c49a7a9f3359355e7266e35760e507cbcb27b09e0cb91d4b7efJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2t4LUh1YW5nL0NoYXRHUFQtb24tV2VDaGF0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b9c3ef423e8928165127a82d0d7c3bfae0153748964e913047c248b7a56a0e2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzYwNjc1MDc1OA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef0c293482cdc5a473b3b5df122f7491b7970504e510fc002aea8093226775b9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9jZWxscGhvbmVzLmNvbS52bi9zZm9ydW0vY2FjaC1kdW5nLWNoYXQtZ3B0LXRpZW5nLXZpZXQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4abb6b477c7a5c192485bcdf242eccb29436a87fc7db2e39ffeb096bfb0afd6bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzYyMjIwNzk1NA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8b96998e95bb0b58ff2f55901a4ad7657f1d718946f44c96c769f43e0a8a836JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9kb2NzLmdpdGh1Yi5jb20vZW4vY29waWxvdC9yZWZlcmVuY2UvYWktbW9kZWxzL3N1cHBvcnRlZC1tb2RlbHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9238f03f5911eba45558523160162fb49ff95ca680b8b9a9ce6ce29c13eb0e07JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9kb2NzLmdpdGh1Yi5jb20vZW4vY29waWxvdC9ob3ctdG9zL2NvcGlsb3QtaW4teW91ci1pZGUvY2hhdC13aXRoLWNvcGlsb3QvY2hhbmdlLXRoZS1jaGF0LW1vZGVs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=922b3e78fc90be0f40a97217a52088eca866e625747e05fe1085c0d7dda62f26JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9jZWxscGhvbmVzLmNvbS52bi9zZm9ydW0vc28tc2FuaC1haS1oYXktdmEtY2hhdC1ncHQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6678ebbf508f8c3da851bdbaf12fbee3b8938b4a1bb75f3defc87c857a79ab8fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9naXN0LmdpdGh1Yi5jb20va2V0dGxlMTEvMzM0MTNiMDJiMDI4YjdkZGQzNWM2M2MwODk0Y2FlZGM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f61a40d18fc894d00477d7daf48cab95c652fd207afac74f827cfd09c13db717JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ab449f9-5b47-68e8-20c2-5e155af569a1&amp;u=a1aHR0cHM6Ly9naXN0LmdpdGh1Yi5jb20vY2hyaXNnaGVyYmVydC9jNzM0ZWM1MGFlNDY0MTM1YmU1N2NkMDNiODQyODFmOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecdccb5f3d5ccb319de20b4da1e7a9d06e3de5f5b584a7526e47b60ef5887506JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bbfadce-64c1-6e07-2913-ba2265136fa3&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzEyNDAyNTg2MDk4NjE2MjE0NTkuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=911009dd760bcc176fb0a42b1e6fbe71290bbdf59fd94f55d7624fb7b986321aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bbfadce-64c1-6e07-2913-ba2265136fa3&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM1NjI5NzE3MA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76d9acf9763fbe27f41905e326e2468638866913558eab556de5f9717924dc70JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3bbfadce-64c1-6e07-2913-ba2265136fa3&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzE3NjAxMjU4NDE1NzY4MjE2NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1abc4a0aedb0fac07b7465bd2ef171253ba10f38bf8998d26750a3cf6fdf932cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ee19245-7393-6307-2ba7-85a972c6621c&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzM0NjA1MzEvYWxs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14fe7e02b034aba2eeae99ccc57be5ca551386fadb52e48fe7859478edcddee7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49a7c117f6dc994975d399b3fec7160f08300e5bc1096c2f04298c4211584255JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZXMtZXMvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f1b4573313970aaa64f275c657b718d1251bfb6075e6784d958f5819ea5a660JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tL3Qvc2hvdy1vci1oaWRlLXByZXZpZXctcGFuZS1pbi1maWxlLWV4cGxvcmVyLWluLXdpbmRvd3MtMTEuMTc3Ni8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96f11a266692e75ec614c29b657360331dde23444d96074e7bcb7557e5673ff9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tL3QvaG93LWRvLWktYnJpbmctYmFjay10aGUtb2xkLXdpbmRvd3MtNy1maWxlLWV4cGxvcmVyLWJhY2stdG8td2luZG93cy0xMS4xMDYwMi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aea76843f4f7aa983697a644d7211baed7d040dd6bb688606716b448b99e6365JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dfc4dd57da1b152f2d1a06a3f257f6f570760f423d7b2db2a2bae64e47000fefJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97b2e27c658d3c8b5dbaaf6ec525d3474271f1deb52e6e19dba1de1bd867a07dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vaWQtaWQvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d6a5fdbc16f52e52b7e01632d330473369663773da8784580655d9161d699e5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maXgtZmlsZS1leHBsb3Jlci1pZi1pdC13b24tdC1vcGVuLW9yLXN0YXJ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c969fabc3d7990759418a30ff34953890a9554a9f3281fc48fd883d925e13c24JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vdmktdm4vd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d629fb8493c94c2c02cbb231b3443df152e598a5fc8772fe88592f113e955d1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133f1730-1b68-6b78-0e70-00dc1afd6a7d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb25lZHJpdmUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70bc6517c3d5ac4e4874f81ea40fa10b9a6bc56884f68341ea69369658d900b8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZ29vZ2xlLmNvLmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a14e14d5097d5c372dd7dbdba6b751f7a74748202e6caa24b2aa1ee6b670edeeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvLmluL2RldGFpbHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=911682244c576fc9d4aaf390c4d2d60f94e61e75bbe36472babd4d4ebb25c719JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9tYXBzLmdvb2dsZS5jby5pbi9tYXBmaWxlcy9ob21lMy5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bf2c22656f9942e2558aa3b54cc724acf70c71f3c0f52c69ed09785e3f9d4d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvLmluL3ZpZGVvaHA_Z3dzX3JkPXNzbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f9b7ca88dee84b5d88a3dfd3582d10c806d09c153e3e62aa8e3a5b72cf0ccaeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvLmluL2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=060f993a915662c6c8e6cc8a3685e152b2b1fc860031667a5cbd60c8aef6dfadJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9lZHUuZ29vZ2xlLmNvLmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92eecfef3d7d715ce353d0fc0d27c87d423f06dc41bce9fdd9c2ca726cb71ae9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9ib29rcy5nb29nbGUuY28uaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad8a6c2674b9b813242030a33695042260016a66fdbbdf9d91b1b0d0dea9538dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9waWNhc2EuZ29vZ2xlLmNvLmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46d1879f962c59b06dc532880e7d545220fa6d6a2242d3d4232750f83e5b2950JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03f58b22-696d-68a1-172c-9cce68416903&amp;u=a1aHR0cHM6Ly9hc3Npc3RhbnQuZ29vZ2xlLmNvLmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4b201a096deda2b6f522fad7239737ced99aad44943b054200baf64fe944ee9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTIzNjE5OS0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f9eae7fabb315b2cad0708089f39165fcc44f7f36b9c1b1d462df527903cc03JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTMwMDAzNS0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e06b2753664e60ecdbfbc559f6098112c24272f7eff4c2c86c26baa37b67055fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTk3MDY3NC0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0860e596930f8ddc6b618d7274f64da75ba69cb46d9c1d59b9c65773dbdfc822JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTI5MTQ1Mi0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f89f00bf1d82683b8eda6d5c73494cdc71fb4eab4461ecf6c1fcb58135190225JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTM3MzQzMS0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0272e9e6b2fda9167f63c0c6a8f563491d3c5b2eadcc01d5eed74e30db316fa9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTkyMDQyNS0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62b94a58fa50551e96c1323fd3d5ea86687b849fffababb1e83cf3598c2dd2ffJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtODE0MDQ3LTEtMS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa2be10c336f413fdfbfaa06fabfb5331612f48c77b762ec36940c9c234d926cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTg5NTYzMy0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c17d1ddacb080265cb38ed347d6bc315b397a4d6e8319aaf338c859bee85c14dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMjEyNjg0MS0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c28c6c5fd191ca372703b8bf1061e5a1706f0ad58a395abc2efc0f4b9730d7dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b1015d0-3d70-69e2-3b39-023c3cb968fd&amp;u=a1aHR0cHM6Ly93d3cuNTJwb2ppZS5jbi90aHJlYWQtMTcxNTc1OC0xLTEuaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4d82158287f63383310b25347eb68df0ea2e080c80253c00f273540acab46b7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9iaXppdmVyc2UuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35bdc5178fb07b547f5fac41474a3b573c38465edf3d88e2d9ef9666145b5fddJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9iaXppdmVyc2UuY29tL3N1cHBvcnQvVHV0b3JpYWxzLzMwMDUucGRm&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5edcf5f7c0c494ef6e7c301102500cad7d8e07f9de3c3cac8f72bbe09569e744JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9zdXBwb3J0LmJpeml2ZXJzZS5jb20vTEVJUC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3276c6d1cb2f32184201554d467a55067adeb51ae3e866b6fe21011e947b873eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9zdXBwb3J0LmJpeml2ZXJzZS5jb20vUmVmdW5kUG9saWN5LnBkZg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3c674e836d2d29b89558a04b980f4c0e0f52eef67ced67c7d002ba38c35d7c4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9iaXppdmVyc2UuY29tL0hlbHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2b525c890a6175a8ce29beb8aca5b4caffad1980d4caa48b8b602da8285f5c1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9iaXppdmVyc2UuY29tL0FwcEluZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=206b493bc9ba64e616c6d87ed04129e7d5657b7639e2f95d2cbfd80be8316655JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25e02879-cca4-623d-1f6c-3f95cd2d6334&amp;u=a1aHR0cHM6Ly9iaXppdmVyc2UuY29tL1BheQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6eaa8560bee6c29741a684e537b2c8b5a1bbe13889cce8eb3eda73e960dbb973JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa5a720-301b-61fe-1e0e-b0cc316f6066&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tL3Qvb3Blbi1maWxlLWV4cGxvcmVyLWluLXdpbmRvd3MtMTEuMjA1OTEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82d6055317f8d349fdf232c951d80a8c1cb3243194be5d48ab44193fde6903adJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2aa5a720-301b-61fe-1e0e-b0cc316f6066&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vemgtY24vd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d723fd974677fe4497a6a844ade0fa2e35695217742ed6ec90ceba7ef94a4871JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=231594a0-bf97-6816-0306-834cbe85699c&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2d3ee7bd155b700eec5e5db8dd2bf8265130fb7e2a8a680c18d893ca1260662JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vdHJhbnNsYXRlL2Fuc3dlci82MzUwODUwP2hsPWVuJmNvPUdFTklFLlBsYXRmb3JtJTNERGVza3RvcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abbc514d68dc17adaf4193f8d20a517db42c23199169754f6e4b026a2217db4fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMTMwMzAxNTMvdHJhbnNsYXRlLXdlYnNpdGUtdG8tYW55LXNwZWNpZmljLWxhbmd1YWdlLW9uLXBhZ2UtbG9hZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c78cee89bcf95900763f334d18b47c6967100865c48facc21bd5bf64e133ed78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzQyOTM4NzUvaG93LXRvLXJlbW92ZS1wdW5jdHVhdGlvbi1tYXJrcy1mcm9tLWEtc3RyaW5nLWluLXB5dGhvbi0zLXgtdXNpbmctdHJhbnNsYXRl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=356dab563ddc9c6004da4bb332f55d30f1d9dbb0224756f8133386e8028c4c45JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vYS9hbnN3ZXIvMzM3ODY_aGw9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f02789d6c9a8c8e3f57a32729a02373dc357f99e19dd3d5a9f5fcfb91a0b301JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9qYS5zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzU1MDQvdHJhbnNmb3JtdHJhbnNsYXRlMTAlRTMlODElQTglRTMlODElOTklRTMlODIlOEIlRTMlODElQTglRTMlODElOUElRTMlODIlOEMlRTMlODIlOEI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=512eb3072d2b9bd762fe7790187fe6325f63bbaef16c25e7f5338efa64f12ab6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly93d3cua2Fza3VzLmNvLmlkL3JlZ2lzdGVyL2dvb2dsZXJlZ2lzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42f027c56ad7052b7389e16da77ebf9c37db63ad30ba77568ceadccd33adaf78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDU4NzA1MTMvYW5ndWxhci1uZ3gtdHJhbnNsYXRlLXVzYWdlLWluLXR5cGVzY3JpcHQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9eeb22e50571e345460d09694a2cea34a6277933e89f7c99dd3c0cd3a78ca049JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMjA3MDc5OTEvY3NzLXRyYW5mb3JtdHJhbnNsYXRleS1mcm9tLWphdmFzY3JpcHQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ff69616e030709631194e2ef05265d50b4f4cd78c29785abd5e33703bf7352fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDYxODQ0NTgvdHJhbnNmb3JtLXRyYW5zbGF0ZS01MC01MA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf4e43b9298500fc6f2a26c1483f9b9c6996693af57e061a1ff0db049e3f49e0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f688b33-b553-6585-3992-9cdfb4bd64cf&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzM3MDYxMzIvaG93LXRvLXRyYW5zbGF0ZS1vbmUtbGFuZ3VhZ2UtdG8tYW5vdGhlci11c2luZy1qYXZhLWNvZGU&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86922fc56993bcb3a16b487a3438550a1d700d8e40586ac4a0b05ac58abf31e5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj13TWNxNElPa2NlQQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f710e5e71483cc579b5abb98c854de61ddbeb8124ccddaccd011877cc9ce0e5dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzODY5Mzg4OC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca8db0234a7e74973304f366fb13f0553ad7927258bd6aa2a59f4f0b8d7265b4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1qWkVBMm1Nd0wxaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ed645a9aa8ee7f54c26a9161aadb6be23fe58a4c6f7e7103381f901bfadb655JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90868e39d9da8de7088e858536e5e74c87b0ccd9d67beb9218565cf7070a6dd1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91dGhfKDIwMjZfZmlsbSk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0bdb7191b2507914a4b3521dfebaa77f2699d5e56002a022ad2cec0673ce21JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cuaGlnaG9uZmlsbXMuY29tL3lvdXRoLXJlbGVhc2Utc2NoZWR1bGUtZXBpc29kZXMtY2FzdC13aGVyZS10by13YXRjaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=264935ad2eb24b34edabcdbb0482be5e37ef55acb9be5cce671fa99faae021cfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly9teWJoYXJhdC5nb3YuaW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c138e3afb787fe46a0e88ebe79e6bcc1660b9a4c2249597f1ad6c6d3de0d5eeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly95b3V0aGh1Yi5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c0818a16f36646e9836e1da1e4f9e7ff389892d1eb1dd8b1a4cb6fdb9f63875JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODI3MjM4NTU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be58926da0c0ca7a2dd7a65de8671301d14c4be0d2041f919f875ca516b9376bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=295ab453-fb9b-6988-1ba3-a3bffa126842&amp;u=a1aHR0cHM6Ly93d3cubW9zcGkuZ292LmluL3NpdGVzL2RlZmF1bHQvZmlsZXMvcHVibGljYXRpb25fcmVwb3J0cy9Zb3V0aF9pbl9JbmRpYV8yMDIyL092ZXJ2aWV3LnBkZg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5766ffab5526f5153965a836c1e37b67824290352b73e67228b86bc660daa440JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2hlYXIteWUtaGVhci15ZS1sb29rZS1hdC15ZS1vbGRlLXBvcm4uNDA5MzI5L3BhZ2UtNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ecb190b7ec726834a397b1af58af44c94f359a9c3fa015faeb7dd636affabd9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL3JlYWwtaW5jZXN0LXN0b3JpZXMuNjM0NTQzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0bdac81e618c3be5282f4296ebecfb2d59e76c8257065b4260ee774f14c6f46JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2ZhbWlseS10cmlwLXRvLXRoZS1udWRpc3QtY2FtcC1wYXJ0LTQtbW9tLWFuZC1zaXN0ZXItZGFkLjI2MDEyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7c626443e9b06630b90bce9ce99a0c79f83d12e71aa8cc1316ec00a1c8f0f4fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2dhYmUuNjU3MDEzL3BhZ2UtNQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1927c7ffa74ece8fcc3e11878bb1aa85de64a718296d9aaf2449c92467856353JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2NoaW5lc2UtcG9ybi43MTI0NzIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d3f7729c4aba549301b4182951cfe992ca188a11840fb3762f38c4221a69068JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL3Bvcm4tY29taXguMzIyOTE5L3BhZ2UtNzU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ffb55a90a10fb31e0a4399811ba5610268c49dcdd06b6296266d5fd1718c28eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2phcGFuZXNlLWluY2VzdC1wb3JuLjQzMDM5Ni8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b27e36dd9cfb065632f82b9b736a171b539e742e7112fe81a84ee516cbd22a5cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL21pc2hlbGwtcy12aW50YWdlLXBvcm4uNDE3NzE1L3BhZ2UtMTQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e358bdb103fb790de29e1c30bf52b4c8e47ac5e05aadd483362afb1a7988b85JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL3doby1pcy15b3VyLWZhdm9yaXRlLXBvcm4tc3Rhci40OTA3OTcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37f84a5dab0c0cd5a41205a42ad501ca3685d4f39471d7ce5983a8cc1d3d8201JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22037d90-cbb3-6646-0394-6a7cca3167dd&amp;u=a1aHR0cHM6Ly9mb3J1bS54bnh4LmNvbS90aHJlYWRzL2Z1Y2tpbmctZ2lmcy40MTE4MTYv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cbf559ad4e894f698381a87a1ad8d15e675ee0ebaa5e90b5e9e981a69cdddd51JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfKGZpbG1fc2VyaWVzKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7c279be07e5663995858c305d463b8a49f87cc5fe868e4ca89e5561366dc896JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L3doZXJlLXRvLXdhdGNoLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38fdfc69806eabc69d360eb30b57cfc8a1690e85fa6e6f221cd99d9658d413c1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cubmV0ZmxpeC5jb20vdGl0bGUvODAyNDQzMTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7cc9c8c7bc3477ed77a997692b458747e064de6111a4e8d3722870bf2684b226JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cuanVzdHdhdGNoLmNvbS91cy9tb3ZpZS9hZnRlci0yMDE5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=158cf0263b68e493c9b2a7aa5f1c50653f2376e9a9d3af89ec9be984fd2f074bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly92aW1lby5jb20vMzM2ODUxNTI2P21zb2NraWQ9MTMxZDg1YWUyODNhNjNmZDIyYmM5MjQyMjlhOTYyNzI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=582d14dcf663269b728b78bf0aaebdf92819b9f30d4b6356d9e785779a39fc83JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly9tb3ZpZXdlYi5jb20vYWZ0ZXItbW92aWVzLWluLW9yZGVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a41d2bf6e6523449a3eefb2f6fdd3a5dda3c37682d0653c182d966292f1cbcdfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ0MTI2NDc2L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=983ebc4e7228b33a4004a42dbb40e31f1aa5f1bf9eb50d981da9d314c73091acJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQWZ0ZXJfJTI4MjAxOV9maWxtJTI5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f9e8ebdabafc279c399ac1f91fa24882e2ba850f195023f7fb6f4a7bb000bdfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vbGlzdC9sczUyMTQwNjQwOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=478e73fc73c897fe64b87bbc5682607f061f48d6534d140041653a644395c1afJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=131d85ae-283a-63fd-22bc-924229a96272&amp;u=a1aHR0cHM6Ly93d3cubW92aWVmb25lLmNvbS9tb3ZpZS9hZnRlci9tYlY0YmNFR01KWlpnTUdWd21ZTzk2L21haW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8642dd650ceab0142e2196155521ce68890cac7116dc50c5f8e8d7e1fc84333dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c8e344c64be7d04d71a5cb253ed025ba2cb2457aa38cc4c878e5ba21f03ea11JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeS9uZWVkLWtub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe9c34a3d14416be516d713ca7a67f4c2c4d0192fa2e61a7282990f88f54e1a6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvbGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0454aec3f40be32ad0fd3c3107ac10c21c2af78ea52799b0bbd81175c5ac185JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly93d3cudW5lc2NvLm9yZy9lbi9saXRlcmFjeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a5058d379871e292e84ba17959fa2b94d5019315778eafbbc93a2922f2d920aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGl0ZXJhY3lfaW5fSW5kaWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e7f824e8667b3d8125378680a5192dc2c006d5da783e68c2a21a481601c964bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly9vdXJ3b3JsZGluZGF0YS5vcmcvbGl0ZXJhY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7bc828a9ace9926803465c06b7b0d413aa6ae4700407eedd5e48d38d801c932JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2xpdGVyYWN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a302e87d5011fbd35cf26066bed629d6b8363fdd6b13f90c723acc06a41aac4aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly9saXRlcmFjeXRydXN0Lm9yZy51ay9pbmZvcm1hdGlvbi93aGF0LWlzLWxpdGVyYWN5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09bd1679767a0ced93f5de52fff353e8a0c3aad507c8f48f7ec941e306958ce6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly9pbmRpYWNlbnN1cy5pbi9saXRlcmFjeS1yYXRlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3ad5cb26ef29adef02301b8f37b26790e96e7a88b23b4f42fdb432a92486be4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0225972a-d8bc-6a29-11e7-80c6d9166bba&amp;u=a1aHR0cHM6Ly93b3JsZGxpdGVyYWN5Zm91bmRhdGlvbi5vcmcvdGhlLWltcG9ydGFuY2Utb2YtbGl0ZXJhY3kv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21cf8263948aaf4db5672bb8fadc3ff827377cb07186aebadcb610b4c2eb4ae6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTA4MDE1NDM_aGw9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=927abc4fcfac22fa7999cf8b990c4113ac4bb91fb7695d707d6ca22e135ae75eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZXR2Lz9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=123b1037de55b6a074f3a459b7c7e23a0c3c142c7398ab080a42cca5a5c7c56aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzE5MDMyMzE3NzU5ODA5MTMwNTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd949b6092e7d8d50af73bad1e8846f71aaaf6885239c62863e4d02e77f13917JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzE5NTUwNTMyL2hvdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7459b94c70b0d08558df059ecbd12c6f586e0a94d988cae03e3a1f58004c02aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvNTc0MDc_aGw9bmwmY289R0VOSUUuUGxhdGZvcm0lM0REZXNrdG9w&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98014f1e1cfa4a9611acaec12727baa3ca51b2f1d8f563f28ac93c8fe143f2d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTY0Njg2MT9obD1kYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=847a719d1358091a36f3bddc7c1a696c65345f7f849937f3e118015aaf34e4f9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2cf1feaae92031fbd277d979ffa04eece56508a4a030ff6a3ec73455696ba663JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9cm8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2273e8ff5dceed43c2729b4513dc426a0c0e8545cd7f430cc733c425170e8d4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9dmk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7179bf13e2a07f75fcef7990035916eec4548de9b1015877d352392e0af0120JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b4aa290-2750-6fe0-0c1c-b57c26216e80&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvNjE1OTI1ND9obD1ydQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a15241906548b2bf733df5b38c28def7daef15ead8a348e2e9386ba78979521JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly9lbWVyaXR1cy5vcmcvaW4vbGVhcm4vd2hhdC1pcy1sZWFkZXJzaGlwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e226ffd237222215cd8fbe573f3d2a8816d964d43c45e5e14ffa18caeea115abJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL2NoYXJhY3RlcmlzdGljcy1nb29kLWxlYWRlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eea8e432a325f9cf6100d0c02dc1214a6a4672809caac0b2dc31ca1a899f6158JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MZWFkZXJzaGlw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc45a1d9dd529598f36d9fc56fa5e147fa77c31b70ab8cc683ba65154325534bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cubWFuYWdlbWVudHN0dWR5Z3VpZGUuY29tL2xlYWRlcnNoaXBfYmFzaWNzLmh0bQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f5a0614877cf1c589c7debe5a5299f4ccb643fcb02e660b75db4a9299001beeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cubWNraW5zZXkuY29tL2ZlYXR1cmVkLWluc2lnaHRzL21ja2luc2V5LWV4cGxhaW5lcnMvd2hhdC1pcy1sZWFkZXJzaGlw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d7496ef252ccf0866d4b86c3d2c7c743489873976deb78c2add8834390b08edJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cuY2NsLm9yZy9hcnRpY2xlcy9sZWFkaW5nLWVmZmVjdGl2ZWx5LWFydGljbGVzL3doYXQtaXMtbGVhZGVyc2hpcC1hLWRlZmluaXRpb24v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa1ecea000817506fb830fb6f18dc99a4881fa784376bf0863530e89cf735ba3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cubmF1a3JpLmNvbS9ibG9nL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=621378806835391c14f50a60df239bd27fd4887823e2e2e92a909c3457b7a6d9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cubWluZHRvb2xzLmNvbS9hMmZqc2oxL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4d8c67d85c75efcdbbe7afcc01a746081523d3976fc65335f41c1b8e0fdf5f8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvbGVhZGVyc2hpcD9tc29ja2lkPTA0MjhhNDhmMTQ2MjY4MmQxYjMxYjM2MzE1Y2Q2OTdi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e16ff49cc9fe3c2b6c7341bbafcab5eb74f3e1b2f568afcfdf1af771f43c4c90JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0428a48f-1462-682d-1b31-b36315cd697b&amp;u=a1aHR0cHM6Ly93d3cuZ2Vla3RvbmlnaHQuY29tL3doYXQtaXMtbGVhZGVyc2hpcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c19d46d730b76e37792e47e7c532c3ffd69fefc354206dc0183dfe7cc7576668JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly83ZGF5c3RvZGllbW9kcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fab7b73ab778858867c003ba09977f3237dec6be950711a0a47d0d86e519c2caJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly93d3cubmV4dXNtb2RzLmNvbS9nYW1lcy83ZGF5c3RvZGllL21vZHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9bdd5cccdfa741bdffe5e82f9671fb6acc5312614c944e5592828f3b3b6e559JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly83ZGF5c3RvZGllbW9kcy5jb20vZGlzY292ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9face172308845f366f471ee6d8e558899939e37a7dd84281526bb1e00974851JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly93d3cuY3Vyc2Vmb3JnZS5jb20vc2R0ZC9zZWFyY2g_Y2xhc3M9bW9kcyZwYWdlPTEmc29ydEJ5PXJlbGV2YW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ff0d8dd472d8bc922cdcde730225f21cdf46c5366f4f7a2a929739b1887e37bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly93d3cubmV4dXNtb2RzLmNvbS9nYW1lcy83ZGF5c3RvZGllL2NvbGxlY3Rpb25z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8900685b5f682944eda940b4724ab1b08640ff3f365d0b71c25440aef60a531JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly93d3cuN2R0ZC50b29scy9tb2Rz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c092eef696374a5d3efdeb9ed589826a32f145c2d0c8132fddd8941a94aebd55JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkudGhlZnVucGltcHMuY29tL3Jlc291cmNlcy9jYXRlZ29yaWVzLzctZGF5cy10by1kaWUtbW9kcy4xLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfd92931f1f10ce08effe4430c4be34ec52cbf894d674a25752aad2aebebcee0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cHM6Ly83ZHRkLWxhYi5jb20vZW4vbW9kcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=628db0997743ab1addbae4cf56e5d106a5aabaf13a6aa233e78442ef8a8837c0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f0ff577-9662-6127-3471-e29b975e6023&amp;u=a1aHR0cDovLzdkMmRsYXVuY2hlci5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fc156db1f7461ada65b846539c0b620b230744816d853191daf90b6f2cdeb60JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly9sZWFybmVuZ2xpc2guYnJpdGlzaGNvdW5jaWwub3JnL2ZyZWUtcmVzb3VyY2VzL3JlYWRpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e798391ae9ea0f304d8af33fbbce344cb4fe53687e2d4473d4bb9e9c1f31b05fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28f9083261cff645ce64ef8ea2e7d961d1f0fc941575cc0108945bb7febb5c1fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmVhZGluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02f4ebf469bacce5d92dfb08a5a8d2370c2608a15282115417f1f49f4c2159e4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGlzaGNsdWIuY29tL3JlYWRpbmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f09b6c2e6af2d291fd9606a08250cd24586950cff699262132c002f67bdf0c8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL2xlYXJuaW5nZW5nbGlzaC9mZWF0dXJlcy90aGVfcmVhZGluZ19yb29t&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09a698515f6ee98408acd6825456603d965245dbd105260a7cd19de4ee03fd58JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly90ZXN0LWVuZ2xpc2guY29tL3JlYWRpbmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e81bb5c990d52f2b6272fcbdf7d444e5b89bf8692290e3b73b429f2a6185961cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly9saW5ndWEuY29tL2VuZ2xpc2gvcmVhZGluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c385c4e892c1bd0fb17502997684c7884c78b2477ef9c19da168a222f16be439JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly9lbmdub3ZhdGUuY29tL2llbHRzLXJlYWRpbmctdGVzdHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ccf7c44b2b86e8610e7c64e7b91e37895593495eb243dc65083069412f2f0a6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly9vcGVubGlicmFyeS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d93d6d113539fd9307443e653ca35ee52aa74c71eb2e1b6638506df432d4fae9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=324c5133-e4d5-6455-2700-46dfe53b659d&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ2Etei5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f0dddeb4cd9a653f723c6bebbaf7ccde50f1231acfc7d7b71b4d96ede30c85aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FZHVjYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc0761bf73d318fc13cd2a7dbed8216e401e0229d4afd91d8f895cc8d3708872JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmdvdi5pbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4c253ca13442cfcff9f77dd6374be34cda4917cfaac77a75f88f3614a480b0eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VkdWNhdGlvbmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7879ce66ecc106401b95f1ea9d006887f1a075088e5b95a23a4ae48ccd3d2fffJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cuZWR1Y2F0aW9uLmNvbS8_bXNvY2tpZD0xNWJiNGQwNzQwNmI2NDMwMTA4ZTVhZWI0MTBlNjUzNw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72d737c34704b4df333cba640acc9250270dff836f60996cb3a083790d49a653JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VkdWNhdGlvbmFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1d43641f7f1adeebdadaec015deefa3f6a22dea132561d21738dacbe0ac8b48JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS9lbi9lZHVjYXRpb25hbD9tc29ja2lkPTE1YmI0ZDA3NDA2YjY0MzAxMDhlNWFlYjQxMGU2NTM3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a89a794eabbff2fc5223ee6514bf7d0ff43342f02f716f08740de0ca9cb6fdbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb253b3JsZC5pbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aeb3e8df02f27396c5d794d9a7072fd361b6fdd269e039344d4681c1e1e2cf94JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZWR1Y2F0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba45aad1994f4cb3fd3f777ec2f388e5169ee8d2c0e3ccae671120c14586bcc2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cuM3VuaXZlcnNpdHkuaW8vbGVhcm4vZWR1Y2F0aW9uYWwtcXVhbGlmaWNhdGlvbi1ndWlkZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c68b17fef889c8eba78025dc22e57082e4afd6dd72e71124045c8961ade32c70JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15bb4d07-406b-6430-108e-5aeb410e6537&amp;u=a1aHR0cHM6Ly93d3cuYXNrZGlmZmVyZW5jZS5jb20vZWR1Y2F0aW9uLXZzLWVkdWNhdGlvbmFsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f2fd42b37a4eaa36aff15ddc085252ccc93bc619fa55239ab4e0f913ee5daeaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9jaGF0Z3B0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44ebe69e577441e60d6d293f88ff702223f931c2e8a666252274f60743851d24JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9jaGF0Z3B0LmNvbS9mZWF0dXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4acbc690e1cc0c414a9fa42c1b90482ac7bd1404c1761e9372073316c82597b0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9vcGVuYWkuY29tL2luZGV4L2NoYXRncHQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e79c104e12fcbf263fe3f4466e7552c5f96f1dc363c87a6dd61a81fb26f9da60JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9vcGVuYWkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4aa0d98820a7ffb452f5e3d104eaa79960c42f8f576a4446820f039ae7b8647fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2hhdEdQVA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8e7699b59859367e8c94b32efeee114f1248d13a06f369308da575f2694687dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9jaGF0Z3B0LmNvbS9hdXRoL2xvZ2lu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=751db74381d3183fb95a3c50e9915b8e1f86dbf9ce2620a68f0494282321bb46JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9jaGF0Z3B0LmNvbS9wbGFucy9mcmVlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0005380fd6cdc779c53ba4da5ebcb2acc770dde9c2aee33a150e05f06fbcd680JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9jaGF0Z3B0LmNvbS9kb3dubG9hZC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d34ff23a1d6f12cbff54dfbaa2ed2ef029975ff8921212db63fc39c48e742365JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13812a53-e346-6046-0507-3dbfe2136190&amp;u=a1aHR0cHM6Ly9vcGVuYWkuY29tL2luZGV4L2dwdC00Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=082862344a271e4cac84718ec36e3524de94d313f27024716aaa41dbbb1cbc52JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2JyYW1zZXMvY2hhdGdwdC1tZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=870c3f31bf2e11d7434c238156e1930ecd06bb487fe67d6d20cdcfde1c67a3d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3Jhc2hpZGF6YXJhbmcvY2hhdGdwdC1jaGF0LWV4cG9ydGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66c94be4bd5be6fe22cd9453ab12c6dffabba49968a2359c63c8fd592c0ccabcJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzI2NjkxODk1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d530f8ec2a0dcd6fe5499eaff36afd95bc2786f20abfe4fa59b793c58e6caafJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NoYXRHUFQvdG9wLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18cab9edaf892ca369bf58b87f3df1c4023441ef34ed9985f743196eccec568cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NoYXRHUFRQcm9tcHRHZW5pdXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0874380b132b7138fdd057d3ae42dc8240fdd423f49606280cc4cc2dcef6b9cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU3MDcyOTE3MA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e7bd98399c655024b1d9109634928cfec20143871c41784d4935ae095208eacJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9kb2NzLmdpdGh1Yi5jb20vcGFnZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffca9b9363132fe349187fc4275f3fbef3fb7dc85fc5cfa0ece17aed1a081aa3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9kZXNrdG9wLmdpdGh1Yi5jb20vZG93bmxvYWQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d87fa5d1653443a2bf31c8abe9e102a5a759ae2412ac3e8b3b2507df5d05befJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL1hpYW9EdW9ZYS9jb2RleC13aXRoLWNoYXRncHQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d47957fa19b94c9b74cc95255993d51f67eb8051030855db0f6aa30bc920be6bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ae9c7ea-fb5f-67fe-2501-d006fa3066f0&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0Z3B0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=098f8e4c37d306778a08cfcc7d92bd63405cb04ad1bd5a5bb703b342f1187319JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuYXN0cm9sb2d5YW5zd2Vycy5jb20vY29tcGF0aWJpbGl0eS9sb3ZlL3ZpcmdvLWdlbWluaS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7937d9b3cb042dfab08a7b1e4cf306fa916a705e008f180e5d34e41f9bb25ccdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNjMwMzM2MDY3Njc4OTU3MzU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9625ec98f83b773cba59249801c977d0c3ae5c43b1dae04e7915a9c65c723d66JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuYXN0cm9sb2d5YW5zd2Vycy5jb20vem9kaWFjLXNpZ25zL2dlbWluaS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=285effebc566e1b154476c4992c62646df08e9d620a3b34ce576b61ef987dc4dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNTA1MjcyOTA5MjUyNDg2Mzc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c41c5aa2c65ae07b3ee909875e68d192144eb5410234bac9b1eae271bbd576b0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly9iYnMuaHVhd2VpY2xvdWQuY29tL2Jsb2dzLzQ1MzM3MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7fa50b3bf011dc360bfd34815e22150ec13a73e66aa0c81fc631c644a785bc7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuYXN0cm9sb2d5YW5zd2Vycy5jb20vaG9yb3Njb3Blcy9nZW1pbmktbG92ZS1ob3Jvc2NvcGUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4107e441ed389269876ce6e15654fa0b59631061a663a1651dbe9438e3050a65JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuYXN0cm9sb2d5YW5zd2Vycy5jb20vaG9yb3Njb3Blcy9nZW1pbmktd2Vla2x5LWhvcm9zY29wZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c056347fe1004e84c95b681cee8a957729bc5aa8af07d3a0c5ed650c5521e04JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuYXN0cm9sb2d5YW5zd2Vycy5jb20vem9kaWFjLXNpZ25zL2dlbWluaS93b21hbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18c2b4b36df254dd63a0c5429198c1c51fb4c67c195264349ccbfdc054c2565fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNzg2MjUxMjE2NDQ4NDUwMzI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a485e3ae76c491c05202026d6b36c8fe0d6c66c27aca78d20b8189e35a028760JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f8a6e72-8887-697f-0190-799e8933680e&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNDAyNTExMzY4Njc4MTU0Njk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6525180d0b611b2868c6a29052227db8d3bf455ab3f9afd2f6cb5da3db91bda7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0aaecc89-59c2-6b23-265a-db65584b6a47&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMjQ3NDAyNj9obD1ubA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfe2cbf1f13e8394debb6cb88c3bfb1c4e93c50e7d98c8cd00647b9ec4e400b0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0aaecc89-59c2-6b23-265a-db65584b6a47&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTY0Njg2MT9obD16aC1IYW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cd6d533ad235444c34b5936115713561fb630a89fbcf1d59bb8606c125b6742JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy0xMi9jb252ZXJ0LXRvLXBkZi1jb250ZXh0LW1lbnUtaW4tZXhwbG9yZXItbWlzc2luZy0xNTE3MDkz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2874a41fc60cec5cb2737cfd683f8238c8c4843abac3820ccb2b7acf7569f532JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy0xMi93b3JkLWZpbGUtcmVkbGluZS1ub3Qtc2hvd2luZy13aGVuLWNvbnZlcnRlZC10by1wZGYtMTUyMzA1MA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864791244ca2d8e9b1a3899796d2fb6c2a6e6e4c04d780bae2bd73843a4c81a2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9hc2t1YnVudHUuY29tL3F1ZXN0aW9ucy81MDE3MC9ob3ctdG8tY29udmVydC1wZGYtdG8taW1hZ2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56056636d024ca36b716f91ca151475de8000d706384b4070bfff539fcfb8b7bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9hc2t1YnVudHUuY29tL3F1ZXN0aW9ucy8zNzU0OC9wZGYtdG8td29yZC1jb252ZXJzaW9uLXNvZnR3YXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0356e0369b62d8ae8396fbfc1899088b90cb09345a4065dd7e0aa2d112291421JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy0yNy91bmFibGUtdG8tY29udmVydC1hLXBkZi1pbnRvLXdvcmQtYXMtaXQtanVzdC1zYXktdXBsb2FkaW5nLWFkb2JlLXBkZnBhY2stNjE4Nzk0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1caa87e9e1fc45176b0586fbcb9932784c2c783ad69a8e88b431058737ee16a0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy05L2NvbnZlcnRpbmctcGRmLXRvLXdvcmQtaXMtbm90LXdvcmtpbmctMTI0NTA2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e96c5aec423298803a0dea4f8a52a2d2fdecefe3f2c84768bb13b11ccdc0ec42JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy05L2JhdGNoLWNvbnZlcnQtcGRmLXRvLXdvcmQtMTIzNTc2OA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c69f5cb6245089d3039554887cc47822ab52f05a04aa22e82499fada8f442e59JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy0yNy9ob3ctY2FuLWktY29udmVydC1hLXBkZi1maWxlLWludG8td29yZC13aXRob3V0LXRoZS10ZXh0LWJveGVzLWluLXdvcmQtNjE2NzQx&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7527f0cfa6a153523973439eed1ff1121b954b209c5697184431109d1f3a23aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy0yNy9jb252ZXJ0aW5nLXBkZi10by1leGNlbC1vci13b3JkLWRpc3BsYXlzLWltYWdlLWluc3RlYWQtb2YtdGV4dC02MTk4NjA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8227faa2bcf878b488cb8702aa5cff920adbe2d05983aa730549798123643cceJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e0086f-5085-672f-33ad-1f8351566635&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHkuYWRvYmUuY29tL3F1ZXN0aW9ucy05L3JpZ2h0LWNsaWNrLWNvbnZlcnQtdG8tcGRmLWluLXdpbmRvd3MtMTAtMTMxMjU4NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da840bd21a4d5557928e8948016e4b0ed3c0e518d163dfe7516633b3c4c80532JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19b0b232-67b1-68c9-1eeb-a5de665a6981&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5zcG90aWZ5LmNvbS9lbi9sb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8d8be73cf867ce06be4f348ec07ac338a0731140981a7305f1ade4088c224a8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzQ4OTAwODg4OQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf1420f8fdef7699b4f43872dc8fc09ae94ac87dcfb99adabdcbd98344f434c0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzQyMjQ4MzE5NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00ddd2258c623a087427c44d835ffdb24d20acc8738c7cf73a070d9f48c1328aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly9qaW5neWFuLmJhaWR1LmNvbS9hcnRpY2xlLzI3ZmE3MzI2OGY3OWUxNDZmODI3MWZhMC5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95ed3368f181b4f7cffc4cf391d6db17da8badf044ca3fe28d47e2f7639de089JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzYxMzM3ODQ1OQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b668337985473fe41d76905715cc029a829ae685b677aca093328209911e937JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU1NDAwMDAxNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d387a6b5e15e210fc23e9c84ff8b0dca679d7c9f46018f1e7d2469faa7cca901JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzQyMDE3ODE0NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6baf8ac5c448a4dbae4633afbe0467cf0bdb3f4b2c88b8356b8cbda47b45dc42JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIyMTkzMzMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41fa12a13199f2d9220e954eae35d470679cd85e5e1bb502da985bbed0f2cf6bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMyMTcxMzUwOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ac514c8fc5451f97149acec8c666eae7d5a0a4f37e1d5b71f62fb4431b07bdaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzUxMTcwODA1Mg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bc51a8df531e2e100d2fc2d14b4c4b0e2803a9742991e0c2646f183b713604eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a5b1e08-6be9-6b9b-3f5f-09e46a606a37&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzE5MDA1NDc2MTU0OTU1NDUwNTQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8050b5df75991b9b7953618ed0db9353f1c6221aec81835dde1a9da43e242d17JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktR28vU2t5LUdvLVdvbnQtU3RhcnQtdXAtb24tV2luZG93cy0xMS1QQy90ZC1wLzQ0MTM4NTg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df8079586bfa4506d32d974bb6fe8bfffa88c5bd8f10a06b453ea1531729ec5cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktR28vU0tZLUdPLWFtcC1XSU5ET1dTLTEwLTExLUxBUFRPUC1JU1NVRVMvdGQtcC80NTY0NzQw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8eb3c88288ffc64c6cfe5dccbfcc78230ced0fb49eaadec11d1ace53c27c75dfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktR28vU2t5LWdvLWRlc2t0b3AtYXBwLW5vdC13b3JraW5nLW9uLXdpbmRvd3MvdGQtcC80NDA5Mzk1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e652ff960103ba97756b5a762388c12cf71776f28e285510ebef4a5ba9094622JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktR28vU2t5LWdvLWFwcC1ub3Qtd29ya2luZy1vbi13aW5kb3dzLTExL3RkLXAvNDMwNjkyNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=229adc565a500656b386bb0af4a585f2ae590a2531965001431a9cdbd4a4b4a1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9BY2NvdW50LUJpbGxpbmcvYmQtcC9za3l2aXAvcmVkaXJlY3RfZnJvbV9hcmNoaXZlZF9wYWdlL3RydWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28a33956399e0cf4a7b787e25d1940f6b7ffa0c8c093153a81569056be575692JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktUS9Ta3ktUS1Cb3gtbm90LWNvbm5lY3RpbmctdG8td2lmaS90ZC1wLzUxMDgzODU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adcf1f11be42d0072bc425328b596c848236ec96ea4eec41ca03b3f7e6697414JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ccm9hZGJhbmQvSVAtQWRyZXNzL3RkLXAvNDgxMDYwMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aac5b3f0f1d67eacf43922da31c4f427bbcad22bd9ce831c7555b7d5a0f3de97JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktR2xhc3MvU2t5LUFkcy1tb3N0LWFubm95aW5nL3RkLXAvNDgwODQ4NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4239ded201a1d74e933b26b4d67ca62cd75260868918b04c8ca16845027cb0cfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9BY2NvdW50LUJpbGxpbmcvSS13b3VsZC1saWtlLXRvLXNwZWFrLXRvLWEtcmVhbC1wZXJzb24tYXQtc2t5LXdoYXQtcy10aGUtbnVtYmVyL20tcC80NTY2NzMx&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c25dc773db9f0a785440aa74dbc6ae53f2472c9b34a7febfb7a96559c11ae564JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1021d868-0d95-6976-3896-cf840c00681d&amp;u=a1aHR0cHM6Ly9oZWxwZm9ydW0uc2t5LmNvbS90NS9Ta3ktUS9TY3JlZW4tZ29lcy1ibGFjay1tb21lbnRhcmlseS10aGVuLWNvbWVzLWJhY2stb24tYWZ0ZXItYS1zZXJ2aW5nLW9mLXR3by90ZC1wLzQzNDM1Nzg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00d3104f07fa50f2fbce7e4c7ea364c21903f24f397782f3441d4602bce8ae26JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzE4MDU4NjkwNzE0ODA4NjUwNjcuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e71f371a8a13c61e29b74f8308e80d02e081ac9709a8afe5c2148121a5e439dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMxNzQ5MjM5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46458b038e3300728a64a8132230b8e5b23e326e099bfb7c1d8541117d7f0840JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzY0OTc3OTY1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60b8b16aa3608a0a92aaa7202c00931e981f7a511223704011b70bb44994977dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzU3OTA0MjI5NC5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b48d2c7c47a5722c463e4b3cb57be414587c8c36f07c3bbf745f96f3fb48576eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMwOTcxMzcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85f225ee10299a11cbce7d4a042d7905a1184a9eb8d8e78fb5f7c5df39d5a87dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzM5NzY2NzY3OQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d557cb9db918dafe243ec30dbb056c9ea93fa5ea0e2156a7290a3b11bb6642d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzUzMjEwMTA3NTkyMTkyNTkyNS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1d8f0c3c2f8d5369e560c70c1851c026b10aea9ca719dbcdfec5eced86664c1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3p2aWRlby8xMjk3Mjc2NjcxNTk1NjA2MDE2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=393222740d19d8ffa2fb165a093e9c62b5a2fc2f14d6d440a2167145d9eccb52JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzI2NjE4NDEx&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=054e659366c439de99e89d6e99d9ef7d4b1b7d8c18e08959e1576ce023d40b95JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f068fd9-cb67-64a0-1919-9835cae065d4&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzE3NzEwNDQwNDg5NjA3NDcxODAuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7cb7a55ce5676d6df327b4d03b918ea58ee63f78d3d4eb77e5d10d6b3c08b4f9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=349e750b-90f7-6a07-3ec4-62e791dd6bda&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb253b3JsZC5pbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2c69f4d4b6073c9926b6fa7cff77b4468f0ee17e96d019f79eabaeb8acc0e03JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2892fe4fd9818712b160ac264e90f97029c01ee0e00b61071898e1bdcbcdcdc5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1MTk4OTg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=820359c2f6163386d677125aa7984df89867feb8b44c2c945b4a706526e3b040JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjUxOTA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52fffdd89a7db462f16ccf9e99c6ab95db71be5e22b7114831a49d53d1b19d68JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1Mzg3Mzg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eff9672816ad62c389f136a69a8690c123e97a63c67d9892b5c175f6187d0c4bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b6757425182750b8ad45db106c4974e3edc0cef491c1828bf64b694d472ca96JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjYwODA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d17ce56fe8e1497ffab565b546f85db6d3beac876ee26b5802bfb7990817103JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1MjQ4MDY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=832f2168dfb3697de797b8cd9baa5de156bc7c47187b9af2816cccdc5c290619JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzM0NjA1MzEvYWxs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e7318d36cf56a01f20aa4a8786584e838a56dc4f273d8533f62e3d38c6bbd39JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjgyMDc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9c92cbb39a6d1fe283b56588623cffec285e547137d7faa774bc155d3a8868fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0940c17f-f00e-65a5-0479-d693f1ca6405&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NzM2NDM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9495ab3f76e1e241c19b8e46ad70fd63d189ea5dbb2f8b2d7a2e3695efe03b9bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly9nb3Z0am9iZ3VydS5pbi9nb3Z0LWpvYnMtc3RhdGUtd2lzZS93ZXN0LWJlbmdhbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e47f7fa6e5e691efac6a5b9255693e33b0106da73b286179f188c6916cc8d81JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly93Yi5pbmRnb3Z0am9icy5uZXQvY2F0ZWdvcnkvd2ItZ292dC1qb2JzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b57422e9d06a2f9883064ba86094aa8d7eacba24c3205aef50201ed3f8bfaa70JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly93d3cuZnJlZWpvYmFsZXJ0LmNvbS93Yi1nb3Zlcm5tZW50LWpvYnMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d946a04b3c7ebd1e34462d13bb9075ab6703afe5e8354e78bdde4fa8edc1f14eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly93Yi5pbmRnb3Z0am9icy5uZXQvY2F0ZWdvcnkvZGlzdHJpY3QtcmVjcnVpdG1lbnQtam9icy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfc37ed7690b82018789380b5a8ba886df76df97a9071dbb08b9eb12d8008aabJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly9wc2N3YnBvcnRhbC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88b14e0466a2018711d194772f031448bf560fdf69ab917caf5896c64a5961afJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly9wcmIud2IuZ292LmluL3JlY3J1aXRtZW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0a32e564328ccca0759cd4a134134767deb8fa91db3c9b27ababaaa94cd24ddJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly9nb3Z0am9ic2FpLmNvbS9zdGF0ZS93ZXN0LWJlbmdhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d86dc005227e432a19ec42550aff859fc8c84fa40bdf83c816a2c1cddda904a3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly9wcmIud2IuZ292LmluLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd4c075fe7b2b4043136b25d9c20a00572a5661b164f58edb8a10ce1e56635eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3ae0a-2c3c-6cf9-38e1-b9e62d786d16&amp;u=a1aHR0cHM6Ly93YnBvbGljZS5nb3YuaW4vd2JwL2NvbW1vbi9XQlBfUmVjcnVpdG1lbnROZXcuYXNweA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87fc2a578bcc494ef88ddb62c710df4bb6932381d630353e682e3357fa26f244JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=800b326e07182c936608a430a5065a7299007d533d327277c7968644936c87b8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEvY29pbWJhdG9yZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79d7d17e4cb16a6a902bef2b5b524a0481933d9415ec1f6e1317cbe510e59d33JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEvbmV3LWRlbGhp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e740773863f61d15f65b65529edba82378e8957ad2aba9dd33dfd11933573f5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEva29jaGk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2986fc3166aa7e469960ff21cad22c22b4450428c8e872e75cd10e6694dc880JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEvbmFzaGlr&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d938abac5c03ae12cfa0be3489cc1f8cfcbf4ae3e0b6b20e34718c196018a89JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svdGltZXpvbmUvdXRj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33459f164d472e479612eff7764ad2aaa6198b538466b6ea61d4eab6936ef5ceJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEva29sa2F0YQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cf08d1fec86c961c08b54aa933b41ce1e4b2da2a067b7bf8debe53b8387b96acJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEvYWdyYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5683437bb23e4ca72930e61fea1d18e5bf77c4ea167d58e0aff3b153a9b33597JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svdW5pdGVkLWFyYWItZW1pcmF0ZXMvZHViYWk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5e885e7fb00786bac917a0f19f05bdc8245c0aace4c6bb3f700a77ca6de0d7dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1da2b56a-289e-66c1-0ade-a286297f6785&amp;u=a1aHR0cHM6Ly93d3cudGltZWFuZGRhdGUuY29tL3dvcmxkY2xvY2svaW5kaWEvcHVuamFi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62a3b508e222637a4427ff544e7df810fbfc7cb492fd6b7370e7c93f2cb3424dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=107b8063-6a83-6679-3f53-978f6bd16791&amp;u=a1aHR0cHM6Ly93d3cucmVhZGluZ2Etei5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc1d7deb18c420781038a15ac4117dc76743904001d21f79f9fa8f51027aa7c2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NoYXRHUFQvY29tbWVudHMvMTA3emZ4ay9yY2hhdGdwdHNfZmFxX3RocmVhZC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4171de5c7e9db5f10e2a5c9f86b4baa2f83ffb898362a1587156002caa5d2c6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU4NDQwMjMzMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9ea50d8f43768e506d89b5995a9bb1e028ad7aecc0b1f931cdaf44fbbb17d4bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2JhZy14bWwvQ2hhdEdQVC1mb3ItTGVnYWN5LWlPUw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c26e9a6304adc1a04758b3944dc44daba662138586ae515569738d33e8c2697JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0Z3B0LWFwaQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13784fc4e7914a7a7e5f21836e210ed790203024e36c76cb47c4667cfbfd391bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RhaXNoaS1pL2F3ZXNvbWUtQ2hhdEdQVC1yZXBvc2l0b3JpZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50d3d3cd5a84805c04539e0af1a88cbcd2ab0174911446dbc4bb9a1b40d119e9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3495ecba-2052-6909-1857-fb5621496868&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL0xvbmdwYW5aaG91L0NoYXRHUFQtQnlwYXNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22438d865dce5666d3ac53ccb8f90148c0b2eb41b82a2fd86210146e3e4e4230JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93ZWIud2hhdHNhcHAuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ad486fe0c3f19b98de5af580eabb59cf6e806abffc5d011a57e364c481b52f7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93d3cud2hhdHNhcHAuY29tL2Rvd25sb2Fk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=304232ad14b03a68626ad4e2323d5c09ea411f85572b4a858eba489cb54fa8eeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93d3cud2hhdHNhcHAuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=638fc08dd64200d71bfef842beab83e5eb08990d280b786311adc2c4fc848574JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93YS5tZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9031f8b3aabcc066ed46f8fba5bd90c5e9c4c3b6326fc3fcce926e147ac8013JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly9mYXEud2hhdHNhcHAuY29tLzY2ODUzODAwNDY1ODA3OQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d33c0b1ad13a0b6340a870a8e87a99eb76e69f166d934e9b8bb97f8d74eb4700JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93d3cud2hhdHNhcHAuY29tL21lc3NhZ2luZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4624305e4ca6a56d55b4f9aab56729fe4d4fbc1977f1f445c151f82057aea19JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2hhdHNBcHA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c9c6dc731d2358b09ab0098485de2763a659e876ebbf0694075a5e9315ebf38JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly9mYXEud2hhdHNhcHAuY29tLzE1MTM1ODk2OTkxMTkwODA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73ff60c40312b6aa05ea322dc0d46ae790123db948c6c868a1720ce5247fb2f1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly9ibG9nLndoYXRzYXBwLmNvbS93aGF0cy1hcHAtd2Vi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96da6ee60cf9eab4bf5f32352cd5ccf1dd244493d2847c1159c3ff8c1e4c8fe6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38ce84fd-7597-6081-2ab1-931174db61d7&amp;u=a1aHR0cHM6Ly93d3cuY2x1YmljLmNvbS90ZWxlY2hhcmdlci1maWNoZTQzMzAyMy13aGF0c2FwcC1kZXNrdG9wLXBvdXItd2luZG93cy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4721700c230ffc0943371d47dc526e7b71cc1a6fd35a127678508464c61e108JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9UnVsLTB4VjZ3R00&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0e9ba16c544eec23fc0c5ccb494fea4f5a7d774b2bf8ba16ebde36025b47c04JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly93d3cuaW5zdGFncmFtLmNvbS9taXNzX25vYmlfMDExLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67a2b509a02ef26ebc1c4b3df26a652cdc66f1e6588b585c2b96353cbd2202f7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9TGRxSGJucE5ObEU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3183164131418264127017deb9c74b701dd35138429577981f2884c2b34788cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly93d3cuaW5zdGFncmFtLmNvbS9vZmZpY2lhbF9fX19fc2FoZXphZGkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49d3a48986972e40043b2589865b5e14d4ac98872c97adc1e8a0a8ac5f8098e5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9NYW5qYXJpXyhJbmRpYW5fc2luZ2VyKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85d1e3256c0e7cfd37b1d9fc33f94a781d014b23e00195f560733d6cd884f329JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS93YXRjaD92PXRXVFVpcVJvV1A4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a542802d177c498cc411c618a4130b1c2b72225a765bd251d4c57ca2a9d7e84JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3NoZWh6YWRpLm5hYmkuMS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=703dfdaf41e0d30a951cc0b3b792711c5c25826293f971928172dbbb78e541d1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly93d3cuc25hcGNoYXQuY29tL0BzYWhlemFkaTIwMjUw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2263163e95a796e65e6f1b7cc13decf48f236c3ee552cdef0f413f22e76202c3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly93d3cubmFhdC1lLXNhcmthci5jb20vMjAxNS8wOC9zaGVoemFkaS1lLXJhc29vbC1qYW5uYXQta2ktaGFpLW1hbGlrYS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6520a14b2ddba8032f1473010039b3e9bb3eef1e8feca9f05cb0ca43552b2ab3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=165a2563-b3da-636f-02f9-328fb2c16241&amp;u=a1aHR0cHM6Ly9uZXR3b3J0aGxpc3Qub3JnL21hbmphcmktZmFkbmlz&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -1600,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1634,19 +1751,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H2" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1654,19 +1771,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="G3" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H3" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1674,19 +1791,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="G4" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H4" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1694,19 +1811,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="G5" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H5" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1714,19 +1831,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G6" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H6" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1734,19 +1851,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="G7" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H7" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1754,19 +1871,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="G8" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H8" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1774,19 +1891,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="G9" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H9" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1794,19 +1911,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G10" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H10" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1814,19 +1931,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="G11" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H11" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1834,19 +1951,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C12" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="G12" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H12" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1854,19 +1971,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="G13" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H13" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1874,19 +1991,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G14" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H14" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1894,19 +2011,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C15" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="G15" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H15" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1914,19 +2031,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="G16" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H16" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1934,19 +2051,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H17" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1954,19 +2071,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="G18" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H18" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1974,19 +2091,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C19" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="G19" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H19" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1994,19 +2111,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="G20" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H20" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2014,19 +2131,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G21" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H21" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2034,19 +2151,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="G22" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H22" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2054,19 +2171,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="G23" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H23" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2074,19 +2191,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="G24" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H24" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2094,19 +2211,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C25" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H25" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2114,19 +2231,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C26" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="G26" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H26" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2134,19 +2251,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="G27" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H27" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2154,19 +2271,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="G28" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H28" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2174,19 +2291,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="G29" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H29" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2194,19 +2311,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="G30" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H30" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2214,19 +2331,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C31" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="G31" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H31" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2234,19 +2351,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="G32" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H32" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2254,19 +2371,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C33" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="G33" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H33" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2274,19 +2391,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C34" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="G34" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H34" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2294,19 +2411,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G35" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H35" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2314,19 +2431,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="G36" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H36" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2334,19 +2451,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="G37" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H37" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2354,19 +2471,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C38" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="G38" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H38" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2374,19 +2491,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C39" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="G39" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H39" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2394,19 +2511,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="G40" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H40" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2414,19 +2531,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C41" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="G41" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H41" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2434,19 +2551,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="G42" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H42" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2454,19 +2571,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="G43" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H43" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2474,19 +2591,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="G44" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H44" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2494,19 +2611,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="G45" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H45" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2514,19 +2631,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="G46" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H46" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2534,19 +2651,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C47" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="G47" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H47" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2554,19 +2671,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C48" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="G48" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H48" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2574,19 +2691,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="G49" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H49" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2594,19 +2711,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G50" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H50" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2614,19 +2731,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="G51" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H51" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2634,19 +2751,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="G52" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H52" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2654,19 +2771,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C53" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="G53" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H53" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2674,19 +2791,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C54" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="G54" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H54" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2694,19 +2811,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="G55" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H55" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2714,19 +2831,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C56" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="G56" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H56" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2734,19 +2851,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="G57" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H57" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2754,19 +2871,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C58" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="G58" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H58" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2774,19 +2891,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="G59" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H59" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2794,19 +2911,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="G60" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H60" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2814,19 +2931,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C61" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="G61" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H61" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2834,19 +2951,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C62" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="G62" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H62" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2854,19 +2971,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C63" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="G63" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H63" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2874,19 +2991,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="G64" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H64" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2894,19 +3011,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="G65" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H65" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2914,19 +3031,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="G66" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H66" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2934,19 +3051,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C67" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="G67" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H67" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2954,19 +3071,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C68" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="G68" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H68" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2974,19 +3091,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="G69" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H69" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2994,22 +3111,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
-      </c>
-      <c r="D70" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="G70" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H70" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3017,19 +3131,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C71" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="G71" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H71" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3037,19 +3151,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="G72" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H72" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3057,19 +3171,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="G73" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H73" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3077,19 +3191,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="G74" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H74" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3097,19 +3211,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="G75" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H75" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3117,19 +3231,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="G76" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H76" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3137,19 +3251,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C77" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="G77" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H77" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3157,19 +3271,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C78" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="G78" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H78" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3177,19 +3291,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="G79" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H79" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3197,19 +3311,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="G80" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H80" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3217,19 +3331,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C81" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="G81" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H81" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3237,19 +3351,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="G82" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H82" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3257,19 +3371,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="G83" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H83" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3277,19 +3391,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="G84" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H84" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3297,19 +3411,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="G85" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H85" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3317,19 +3431,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="G86" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H86" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3337,19 +3451,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="G87" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H87" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3357,19 +3471,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="G88" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H88" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3377,19 +3491,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C89" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="G89" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H89" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3397,19 +3511,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="G90" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H90" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3417,19 +3531,19 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C91" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="G91" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H91" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3437,19 +3551,19 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="G92" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H92" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3457,19 +3571,19 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C93" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="G93" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H93" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3477,19 +3591,19 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C94" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="G94" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H94" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3497,19 +3611,19 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="G95" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H95" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3517,19 +3631,19 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="G96" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H96" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3537,19 +3651,19 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="G97" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H97" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3557,19 +3671,19 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="G98" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H98" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3577,19 +3691,19 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C99" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="G99" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H99" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3597,19 +3711,19 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="G100" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H100" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3617,19 +3731,19 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C101" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="G101" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H101" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3637,19 +3751,19 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C102" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="G102" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H102" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3657,19 +3771,19 @@
         <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C103" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="G103" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H103" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3677,19 +3791,19 @@
         <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="G104" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H104" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3697,19 +3811,19 @@
         <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C105" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="G105" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H105" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3717,19 +3831,19 @@
         <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="G106" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H106" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3737,19 +3851,19 @@
         <v>113</v>
       </c>
       <c r="B107" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="G107" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H107" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3757,19 +3871,19 @@
         <v>114</v>
       </c>
       <c r="B108" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C108" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="G108" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H108" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3777,19 +3891,19 @@
         <v>115</v>
       </c>
       <c r="B109" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="G109" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H109" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3797,19 +3911,19 @@
         <v>116</v>
       </c>
       <c r="B110" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C110" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="G110" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H110" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3817,19 +3931,19 @@
         <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="G111" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H111" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3837,19 +3951,19 @@
         <v>118</v>
       </c>
       <c r="B112" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C112" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="G112" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="H112" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3857,19 +3971,19 @@
         <v>119</v>
       </c>
       <c r="B113" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C113" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="G113" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H113" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3877,19 +3991,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C114" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="G114" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H114" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3897,19 +4011,19 @@
         <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="G115" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H115" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3917,19 +4031,19 @@
         <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="G116" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H116" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3937,19 +4051,19 @@
         <v>123</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="G117" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H117" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -3957,19 +4071,19 @@
         <v>124</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C118" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="G118" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H118" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3977,19 +4091,19 @@
         <v>125</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G119" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="H119" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3997,19 +4111,19 @@
         <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="G120" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H120" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4017,19 +4131,19 @@
         <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C121" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="G121" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H121" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4037,19 +4151,19 @@
         <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C122" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="G122" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H122" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4057,19 +4171,19 @@
         <v>129</v>
       </c>
       <c r="B123" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C123" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="G123" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H123" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4077,19 +4191,19 @@
         <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C124" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="G124" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H124" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4097,19 +4211,19 @@
         <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C125" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G125" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H125" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4117,19 +4231,19 @@
         <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C126" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="G126" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H126" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4137,19 +4251,19 @@
         <v>133</v>
       </c>
       <c r="B127" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C127" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="G127" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H127" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4157,19 +4271,19 @@
         <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C128" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="G128" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H128" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4177,19 +4291,19 @@
         <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C129" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="G129" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H129" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4197,19 +4311,19 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C130" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="G130" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H130" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4217,19 +4331,19 @@
         <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C131" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="G131" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H131" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4237,19 +4351,19 @@
         <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C132" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="G132" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="H132" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4257,19 +4371,19 @@
         <v>139</v>
       </c>
       <c r="B133" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C133" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="G133" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="H133" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4277,19 +4391,19 @@
         <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C134" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="G134" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="H134" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4297,19 +4411,19 @@
         <v>141</v>
       </c>
       <c r="B135" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C135" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="G135" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="H135" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4317,19 +4431,19 @@
         <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C136" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="G136" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="H136" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4337,19 +4451,19 @@
         <v>143</v>
       </c>
       <c r="B137" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C137" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G137" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H137" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4357,19 +4471,19 @@
         <v>144</v>
       </c>
       <c r="B138" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C138" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="G138" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H138" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4377,19 +4491,19 @@
         <v>145</v>
       </c>
       <c r="B139" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C139" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="G139" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H139" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4397,19 +4511,19 @@
         <v>146</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C140" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="G140" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H140" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4417,19 +4531,19 @@
         <v>147</v>
       </c>
       <c r="B141" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C141" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="G141" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H141" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4437,19 +4551,19 @@
         <v>148</v>
       </c>
       <c r="B142" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C142" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="G142" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H142" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4457,19 +4571,19 @@
         <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C143" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="G143" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H143" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4477,19 +4591,19 @@
         <v>150</v>
       </c>
       <c r="B144" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C144" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="G144" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H144" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4497,19 +4611,19 @@
         <v>151</v>
       </c>
       <c r="B145" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C145" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="G145" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H145" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -4517,19 +4631,19 @@
         <v>152</v>
       </c>
       <c r="B146" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C146" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G146" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H146" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -4537,19 +4651,19 @@
         <v>153</v>
       </c>
       <c r="B147" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C147" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G147" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H147" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4557,19 +4671,19 @@
         <v>154</v>
       </c>
       <c r="B148" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C148" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G148" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H148" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4577,19 +4691,19 @@
         <v>155</v>
       </c>
       <c r="B149" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C149" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="G149" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H149" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4597,19 +4711,19 @@
         <v>156</v>
       </c>
       <c r="B150" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C150" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="G150" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="H150" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4617,19 +4731,19 @@
         <v>157</v>
       </c>
       <c r="B151" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C151" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="G151" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H151" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4637,19 +4751,19 @@
         <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C152" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="G152" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H152" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4657,19 +4771,19 @@
         <v>159</v>
       </c>
       <c r="B153" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C153" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="G153" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H153" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4677,19 +4791,19 @@
         <v>160</v>
       </c>
       <c r="B154" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C154" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="G154" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H154" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4697,19 +4811,19 @@
         <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C155" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G155" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H155" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4717,19 +4831,19 @@
         <v>162</v>
       </c>
       <c r="B156" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C156" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="G156" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H156" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4737,19 +4851,19 @@
         <v>163</v>
       </c>
       <c r="B157" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C157" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="G157" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H157" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4757,19 +4871,19 @@
         <v>164</v>
       </c>
       <c r="B158" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C158" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="G158" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H158" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4777,19 +4891,19 @@
         <v>165</v>
       </c>
       <c r="B159" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C159" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="G159" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H159" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4797,19 +4911,19 @@
         <v>166</v>
       </c>
       <c r="B160" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C160" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="G160" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H160" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -4817,19 +4931,19 @@
         <v>167</v>
       </c>
       <c r="B161" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C161" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="G161" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H161" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -4837,19 +4951,19 @@
         <v>168</v>
       </c>
       <c r="B162" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C162" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="G162" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H162" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -4857,19 +4971,19 @@
         <v>169</v>
       </c>
       <c r="B163" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C163" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="G163" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H163" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -4877,19 +4991,19 @@
         <v>170</v>
       </c>
       <c r="B164" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C164" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="G164" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H164" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -4897,19 +5011,19 @@
         <v>171</v>
       </c>
       <c r="B165" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C165" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="G165" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H165" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -4917,19 +5031,19 @@
         <v>172</v>
       </c>
       <c r="B166" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C166" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="G166" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H166" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -4937,19 +5051,19 @@
         <v>173</v>
       </c>
       <c r="B167" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C167" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="G167" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H167" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -4957,19 +5071,19 @@
         <v>174</v>
       </c>
       <c r="B168" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C168" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="G168" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H168" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -4977,19 +5091,19 @@
         <v>175</v>
       </c>
       <c r="B169" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C169" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="G169" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H169" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -4997,19 +5111,19 @@
         <v>176</v>
       </c>
       <c r="B170" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C170" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="G170" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H170" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5017,19 +5131,19 @@
         <v>177</v>
       </c>
       <c r="B171" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C171" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="G171" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H171" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5037,19 +5151,19 @@
         <v>178</v>
       </c>
       <c r="B172" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C172" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="G172" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H172" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5057,19 +5171,19 @@
         <v>179</v>
       </c>
       <c r="B173" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C173" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="G173" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H173" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5077,19 +5191,19 @@
         <v>180</v>
       </c>
       <c r="B174" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C174" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="G174" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H174" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5097,19 +5211,19 @@
         <v>181</v>
       </c>
       <c r="B175" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C175" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G175" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H175" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -5117,19 +5231,19 @@
         <v>182</v>
       </c>
       <c r="B176" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C176" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="G176" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H176" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5137,19 +5251,19 @@
         <v>183</v>
       </c>
       <c r="B177" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C177" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="G177" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H177" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5157,19 +5271,19 @@
         <v>184</v>
       </c>
       <c r="B178" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C178" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="G178" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H178" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5177,19 +5291,19 @@
         <v>185</v>
       </c>
       <c r="B179" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C179" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="G179" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="H179" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5197,19 +5311,19 @@
         <v>186</v>
       </c>
       <c r="B180" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C180" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="G180" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H180" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5217,19 +5331,19 @@
         <v>187</v>
       </c>
       <c r="B181" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C181" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="G181" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H181" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5237,19 +5351,19 @@
         <v>188</v>
       </c>
       <c r="B182" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C182" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="G182" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H182" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5257,19 +5371,19 @@
         <v>189</v>
       </c>
       <c r="B183" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C183" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="G183" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H183" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5277,19 +5391,19 @@
         <v>190</v>
       </c>
       <c r="B184" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C184" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="G184" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H184" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5297,19 +5411,19 @@
         <v>191</v>
       </c>
       <c r="B185" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C185" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="G185" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H185" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5317,19 +5431,19 @@
         <v>192</v>
       </c>
       <c r="B186" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C186" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="G186" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H186" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5337,19 +5451,19 @@
         <v>193</v>
       </c>
       <c r="B187" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C187" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="G187" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H187" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5357,19 +5471,19 @@
         <v>194</v>
       </c>
       <c r="B188" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C188" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="G188" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H188" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5377,19 +5491,19 @@
         <v>195</v>
       </c>
       <c r="B189" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C189" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="G189" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H189" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5397,19 +5511,19 @@
         <v>196</v>
       </c>
       <c r="B190" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C190" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="G190" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H190" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -5417,19 +5531,19 @@
         <v>197</v>
       </c>
       <c r="B191" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C191" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="G191" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H191" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -5437,19 +5551,19 @@
         <v>198</v>
       </c>
       <c r="B192" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C192" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="G192" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H192" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -5457,19 +5571,19 @@
         <v>199</v>
       </c>
       <c r="B193" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C193" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="G193" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="H193" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -5477,19 +5591,19 @@
         <v>200</v>
       </c>
       <c r="B194" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C194" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="G194" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="H194" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -5497,19 +5611,19 @@
         <v>201</v>
       </c>
       <c r="B195" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C195" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="G195" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="H195" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -5517,19 +5631,19 @@
         <v>202</v>
       </c>
       <c r="B196" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C196" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="G196" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="H196" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -5537,19 +5651,19 @@
         <v>203</v>
       </c>
       <c r="B197" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C197" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="G197" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="H197" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -5557,19 +5671,19 @@
         <v>204</v>
       </c>
       <c r="B198" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C198" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="G198" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="H198" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -5577,19 +5691,419 @@
         <v>205</v>
       </c>
       <c r="B199" t="s">
+        <v>226</v>
+      </c>
+      <c r="C199" t="s">
+        <v>227</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G199" t="s">
+        <v>451</v>
+      </c>
+      <c r="H199" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" t="s">
         <v>206</v>
       </c>
-      <c r="C199" t="s">
+      <c r="B200" t="s">
+        <v>226</v>
+      </c>
+      <c r="C200" t="s">
+        <v>227</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G200" t="s">
+        <v>451</v>
+      </c>
+      <c r="H200" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
         <v>207</v>
       </c>
-      <c r="F199" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="G199" t="s">
-        <v>412</v>
-      </c>
-      <c r="H199" t="s">
-        <v>413</v>
+      <c r="B201" t="s">
+        <v>226</v>
+      </c>
+      <c r="C201" t="s">
+        <v>227</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G201" t="s">
+        <v>451</v>
+      </c>
+      <c r="H201" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>208</v>
+      </c>
+      <c r="B202" t="s">
+        <v>226</v>
+      </c>
+      <c r="C202" t="s">
+        <v>227</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G202" t="s">
+        <v>451</v>
+      </c>
+      <c r="H202" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>209</v>
+      </c>
+      <c r="B203" t="s">
+        <v>226</v>
+      </c>
+      <c r="C203" t="s">
+        <v>227</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G203" t="s">
+        <v>451</v>
+      </c>
+      <c r="H203" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" t="s">
+        <v>226</v>
+      </c>
+      <c r="C204" t="s">
+        <v>227</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G204" t="s">
+        <v>451</v>
+      </c>
+      <c r="H204" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" t="s">
+        <v>211</v>
+      </c>
+      <c r="B205" t="s">
+        <v>226</v>
+      </c>
+      <c r="C205" t="s">
+        <v>227</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G205" t="s">
+        <v>451</v>
+      </c>
+      <c r="H205" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>212</v>
+      </c>
+      <c r="B206" t="s">
+        <v>226</v>
+      </c>
+      <c r="C206" t="s">
+        <v>227</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G206" t="s">
+        <v>451</v>
+      </c>
+      <c r="H206" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>213</v>
+      </c>
+      <c r="B207" t="s">
+        <v>226</v>
+      </c>
+      <c r="C207" t="s">
+        <v>227</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G207" t="s">
+        <v>451</v>
+      </c>
+      <c r="H207" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>214</v>
+      </c>
+      <c r="B208" t="s">
+        <v>226</v>
+      </c>
+      <c r="C208" t="s">
+        <v>227</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G208" t="s">
+        <v>451</v>
+      </c>
+      <c r="H208" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>215</v>
+      </c>
+      <c r="B209" t="s">
+        <v>226</v>
+      </c>
+      <c r="C209" t="s">
+        <v>227</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G209" t="s">
+        <v>451</v>
+      </c>
+      <c r="H209" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>216</v>
+      </c>
+      <c r="B210" t="s">
+        <v>226</v>
+      </c>
+      <c r="C210" t="s">
+        <v>227</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G210" t="s">
+        <v>451</v>
+      </c>
+      <c r="H210" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>217</v>
+      </c>
+      <c r="B211" t="s">
+        <v>226</v>
+      </c>
+      <c r="C211" t="s">
+        <v>227</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G211" t="s">
+        <v>451</v>
+      </c>
+      <c r="H211" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" t="s">
+        <v>226</v>
+      </c>
+      <c r="C212" t="s">
+        <v>227</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G212" t="s">
+        <v>451</v>
+      </c>
+      <c r="H212" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>219</v>
+      </c>
+      <c r="B213" t="s">
+        <v>226</v>
+      </c>
+      <c r="C213" t="s">
+        <v>227</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G213" t="s">
+        <v>451</v>
+      </c>
+      <c r="H213" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>220</v>
+      </c>
+      <c r="B214" t="s">
+        <v>226</v>
+      </c>
+      <c r="C214" t="s">
+        <v>227</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G214" t="s">
+        <v>451</v>
+      </c>
+      <c r="H214" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>221</v>
+      </c>
+      <c r="B215" t="s">
+        <v>226</v>
+      </c>
+      <c r="C215" t="s">
+        <v>227</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G215" t="s">
+        <v>451</v>
+      </c>
+      <c r="H215" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>222</v>
+      </c>
+      <c r="B216" t="s">
+        <v>226</v>
+      </c>
+      <c r="C216" t="s">
+        <v>227</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G216" t="s">
+        <v>451</v>
+      </c>
+      <c r="H216" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>223</v>
+      </c>
+      <c r="B217" t="s">
+        <v>226</v>
+      </c>
+      <c r="C217" t="s">
+        <v>227</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G217" t="s">
+        <v>451</v>
+      </c>
+      <c r="H217" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" t="s">
+        <v>226</v>
+      </c>
+      <c r="C218" t="s">
+        <v>227</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G218" t="s">
+        <v>451</v>
+      </c>
+      <c r="H218" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" t="s">
+        <v>225</v>
+      </c>
+      <c r="B219" t="s">
+        <v>226</v>
+      </c>
+      <c r="C219" t="s">
+        <v>227</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G219" t="s">
+        <v>451</v>
+      </c>
+      <c r="H219" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -5792,6 +6306,26 @@
     <hyperlink ref="F197" r:id="rId196"/>
     <hyperlink ref="F198" r:id="rId197"/>
     <hyperlink ref="F199" r:id="rId198"/>
+    <hyperlink ref="F200" r:id="rId199"/>
+    <hyperlink ref="F201" r:id="rId200"/>
+    <hyperlink ref="F202" r:id="rId201"/>
+    <hyperlink ref="F203" r:id="rId202"/>
+    <hyperlink ref="F204" r:id="rId203"/>
+    <hyperlink ref="F205" r:id="rId204"/>
+    <hyperlink ref="F206" r:id="rId205"/>
+    <hyperlink ref="F207" r:id="rId206"/>
+    <hyperlink ref="F208" r:id="rId207"/>
+    <hyperlink ref="F209" r:id="rId208"/>
+    <hyperlink ref="F210" r:id="rId209"/>
+    <hyperlink ref="F211" r:id="rId210"/>
+    <hyperlink ref="F212" r:id="rId211"/>
+    <hyperlink ref="F213" r:id="rId212"/>
+    <hyperlink ref="F214" r:id="rId213"/>
+    <hyperlink ref="F215" r:id="rId214"/>
+    <hyperlink ref="F216" r:id="rId215"/>
+    <hyperlink ref="F217" r:id="rId216"/>
+    <hyperlink ref="F218" r:id="rId217"/>
+    <hyperlink ref="F219" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
